--- a/TransactionHistory.xlsx
+++ b/TransactionHistory.xlsx
@@ -9,124 +9,16 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ZzVLD0XOwsrH4caOVTiW91QdZqaIDjktrCTqb9v+e4c="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="0jkq0iH29JNC2PPTsTFBMMBHQJdhwDf2LeV5cgVNLQM="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>Ticker</t>
-  </si>
-  <si>
-    <t>Date 2</t>
-  </si>
-  <si>
-    <t>Price paid $ 2</t>
-  </si>
-  <si>
-    <t>Quantity 2</t>
-  </si>
-  <si>
-    <t>Date 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Price Paid $ 1</t>
-  </si>
-  <si>
-    <t>Quantity 1</t>
-  </si>
-  <si>
-    <t>APT</t>
-  </si>
-  <si>
-    <t>2025-02-09</t>
-  </si>
-  <si>
-    <t>AVD</t>
-  </si>
-  <si>
-    <t>AMPY</t>
-  </si>
-  <si>
-    <t>CTRM</t>
-  </si>
-  <si>
-    <t>CLAR</t>
-  </si>
-  <si>
-    <t>CMT</t>
-  </si>
-  <si>
-    <t>CVLG</t>
-  </si>
-  <si>
-    <t>BOOM</t>
-  </si>
-  <si>
-    <t>EBF</t>
-  </si>
-  <si>
-    <t>ESCA</t>
-  </si>
-  <si>
-    <t>FONR</t>
-  </si>
-  <si>
-    <t>FRD</t>
-  </si>
-  <si>
-    <t>GILT</t>
-  </si>
-  <si>
-    <t>HOFT</t>
-  </si>
-  <si>
-    <t>KE</t>
-  </si>
-  <si>
-    <t>LAKE</t>
-  </si>
-  <si>
-    <t>LSEA</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>NGS</t>
-  </si>
-  <si>
-    <t>NSYS</t>
-  </si>
-  <si>
-    <t>PANL</t>
-  </si>
-  <si>
-    <t>PKOH</t>
-  </si>
-  <si>
-    <t>RGS</t>
-  </si>
-  <si>
-    <t>RCKY</t>
-  </si>
-  <si>
-    <t>SGA</t>
-  </si>
-  <si>
-    <t>GASS</t>
-  </si>
-  <si>
-    <t>TITN</t>
-  </si>
-  <si>
-    <t>VPG</t>
   </si>
 </sst>
 </file>
@@ -144,12 +36,10 @@
       <b/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -401,698 +291,100 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="23" width="8.71"/>
+    <col customWidth="1" min="1" max="17" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2">
-        <v>5.6074</v>
-      </c>
-      <c r="D2" s="2">
-        <v>65.0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2">
-        <v>6.5376</v>
-      </c>
-      <c r="D4" s="2">
-        <v>72.0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2">
-        <v>3.77771</v>
-      </c>
-      <c r="D5" s="2">
-        <v>105.0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2">
-        <v>20.855</v>
-      </c>
-      <c r="D7" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2">
-        <v>22.8421</v>
-      </c>
-      <c r="D8" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2">
-        <v>11.7444</v>
-      </c>
-      <c r="D9" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2">
-        <v>21.3939</v>
-      </c>
-      <c r="D10" s="2">
-        <v>23.0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2">
-        <v>14.5313</v>
-      </c>
-      <c r="D11" s="2">
-        <v>23.0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2">
-        <v>16.8429</v>
-      </c>
-      <c r="D12" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2">
-        <v>14.6853</v>
-      </c>
-      <c r="D13" s="2">
-        <v>38.0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2">
-        <v>5.5757</v>
-      </c>
-      <c r="D14" s="2">
-        <v>63.0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2">
-        <v>23.3679</v>
-      </c>
-      <c r="D16" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2">
-        <v>17.7633</v>
-      </c>
-      <c r="D17" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2">
-        <v>8.3</v>
-      </c>
-      <c r="D18" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2">
-        <v>8.2293</v>
-      </c>
-      <c r="D19" s="2">
-        <v>40.0</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A19" s="2"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2">
-        <v>32.3644</v>
-      </c>
-      <c r="D20" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A20" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2">
-        <v>19.5252</v>
-      </c>
-      <c r="D21" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A21" s="2"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2">
-        <v>11.449</v>
-      </c>
-      <c r="D22" s="2">
-        <v>30.0</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A22" s="2"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2">
-        <v>5.4212</v>
-      </c>
-      <c r="D23" s="2">
-        <v>80.0</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A23" s="2"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2">
-        <v>23.8281</v>
-      </c>
-      <c r="D24" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A24" s="2"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2">
-        <v>24.3206</v>
-      </c>
-      <c r="D25" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A25" s="2"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2">
-        <v>23.0014</v>
-      </c>
-      <c r="D26" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A26" s="2"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="2">
-        <v>19.4371</v>
-      </c>
-      <c r="D27" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A27" s="2"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2">
-        <v>6.542200000000001</v>
-      </c>
-      <c r="D28" s="2">
-        <v>81.0</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A28" s="2"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="2">
-        <v>24.3519</v>
-      </c>
-      <c r="D29" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A29" s="2"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="2">
-        <v>30.1995</v>
-      </c>
-      <c r="D30" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0.0</v>
-      </c>
+      <c r="A30" s="2"/>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>

--- a/TransactionHistory.xlsx
+++ b/TransactionHistory.xlsx
@@ -436,12 +436,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Price paid 2025-02-12</t>
+          <t>Price paid 2025-02-14</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Quantity 2025-02-12</t>
+          <t>Quantity 2025-02-14</t>
         </is>
       </c>
     </row>

--- a/TransactionHistory.xlsx
+++ b/TransactionHistory.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Price paid 2025-02-15</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Quantity 2025-02-15</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Price paid 2025-02-14</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Quantity 2025-02-14</t>
         </is>
@@ -451,10 +461,18 @@
           <t>APT</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5.468811</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>5.6074</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>65</v>
       </c>
     </row>
@@ -470,6 +488,12 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -477,10 +501,18 @@
           <t>AMPY</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5.2800903</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
         <v>6.5376</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>72</v>
       </c>
     </row>
@@ -490,10 +522,18 @@
           <t>CTRM</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.6501873</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
         <v>3.77771</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>105</v>
       </c>
     </row>
@@ -509,6 +549,12 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -517,9 +563,15 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
         <v>20.855</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>20</v>
       </c>
     </row>
@@ -530,9 +582,15 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>22.8421</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>24</v>
       </c>
     </row>
@@ -543,9 +601,15 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>11.7444</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -556,9 +620,15 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
         <v>21.3939</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>23</v>
       </c>
     </row>
@@ -569,9 +639,15 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
         <v>14.5313</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>23</v>
       </c>
     </row>
@@ -582,9 +658,15 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
         <v>16.8429</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>21</v>
       </c>
     </row>
@@ -595,9 +677,15 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
         <v>14.6853</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>38</v>
       </c>
     </row>
@@ -607,10 +695,18 @@
           <t>GILT</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7.4802094</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
         <v>5.5757</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>63</v>
       </c>
     </row>
@@ -626,6 +722,12 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -634,9 +736,15 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
         <v>23.3679</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>19</v>
       </c>
     </row>
@@ -647,9 +755,15 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.7633</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>21</v>
       </c>
     </row>
@@ -659,10 +773,18 @@
           <t>LSEA</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8.120445</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -673,9 +795,15 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
         <v>8.2293</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>40</v>
       </c>
     </row>
@@ -686,9 +814,15 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
         <v>32.3644</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>16</v>
       </c>
     </row>
@@ -698,10 +832,18 @@
           <t>NGS</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>25.769165</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
         <v>19.5252</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>27</v>
       </c>
     </row>
@@ -711,10 +853,18 @@
           <t>NSYS</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10.340195</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.449</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>30</v>
       </c>
     </row>
@@ -725,9 +875,15 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
         <v>5.4212</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>80</v>
       </c>
     </row>
@@ -738,9 +894,15 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
         <v>23.8281</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>21</v>
       </c>
     </row>
@@ -750,10 +912,18 @@
           <t>RGS</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>24.750702</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>24.3206</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>16</v>
       </c>
     </row>
@@ -764,9 +934,15 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
         <v>23.0014</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>21</v>
       </c>
     </row>
@@ -776,10 +952,18 @@
           <t>SGA</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12.729614</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>19.4371</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>24</v>
       </c>
     </row>
@@ -789,10 +973,18 @@
           <t>GASS</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5.6517944</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
         <v>6.542200000000001</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>81</v>
       </c>
     </row>
@@ -803,9 +995,15 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
         <v>24.3519</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>21</v>
       </c>
     </row>
@@ -816,9 +1014,15 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
         <v>30.1995</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>19</v>
       </c>
     </row>

--- a/TransactionHistory.xlsx
+++ b/TransactionHistory.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,20 +436,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Price paid 2025-02-22</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Quantity 2025-02-22</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Price paid 2025-02-15</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Quantity 2025-02-15</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Price paid 2025-02-14</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Quantity 2025-02-14</t>
         </is>
@@ -463,16 +473,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.468811</t>
+          <t>5.401306</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.468811</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>5.6074</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>65</v>
       </c>
     </row>
@@ -494,6 +510,12 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -503,16 +525,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.2800903</t>
+          <t>5.3017273</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.2800903</v>
+      </c>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>6.5376</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>72</v>
       </c>
     </row>
@@ -524,16 +552,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.6501873</t>
+          <t>9.040024</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.6501873</v>
+      </c>
+      <c r="E5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>3.77771</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>105</v>
       </c>
     </row>
@@ -555,6 +589,12 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -569,9 +609,15 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>20.855</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>20</v>
       </c>
     </row>
@@ -581,16 +627,24 @@
           <t>CVLG</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20.295593</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>22.8421</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>24</v>
       </c>
     </row>
@@ -607,9 +661,15 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>11.7444</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -619,16 +679,24 @@
           <t>EBF</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20.568878</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>21.3939</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>23</v>
       </c>
     </row>
@@ -645,9 +713,15 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>14.5313</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>23</v>
       </c>
     </row>
@@ -664,9 +738,15 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>16.8429</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>21</v>
       </c>
     </row>
@@ -676,16 +756,24 @@
           <t>FRD</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10.241577</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>14.6853</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>38</v>
       </c>
     </row>
@@ -697,16 +785,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7.4802094</t>
+          <t>7.0509644</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.4802094</v>
+      </c>
+      <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>5.5757</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>63</v>
       </c>
     </row>
@@ -728,6 +822,12 @@
       <c r="E15" t="n">
         <v>0</v>
       </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -735,16 +835,24 @@
           <t>KE</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>0</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>17.089874</t>
+        </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>23.3679</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>19</v>
       </c>
     </row>
@@ -754,16 +862,24 @@
           <t>LAKE</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13.7248535</t>
+        </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>17.7633</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>21</v>
       </c>
     </row>
@@ -775,16 +891,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8.120445</t>
+          <t>8.549904</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
+        <v>8.120445</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -794,16 +916,24 @@
           <t>MG</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10.086609</t>
+        </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>8.2293</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>40</v>
       </c>
     </row>
@@ -820,9 +950,15 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
         <v>32.3644</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>16</v>
       </c>
     </row>
@@ -834,16 +970,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25.769165</t>
+          <t>27.650696</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>25.769165</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
         <v>19.5252</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>27</v>
       </c>
     </row>
@@ -855,16 +997,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10.340195</t>
+          <t>10.000305</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10.340195</v>
+      </c>
+      <c r="E22" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>11.449</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>30</v>
       </c>
     </row>
@@ -874,16 +1022,24 @@
           <t>PANL</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5.2109375</t>
+        </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
         <v>5.4212</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>80</v>
       </c>
     </row>
@@ -893,16 +1049,24 @@
           <t>PKOH</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>25.398895</t>
+        </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
         <v>23.8281</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>21</v>
       </c>
     </row>
@@ -914,16 +1078,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24.750702</t>
+          <t>26.994904</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>24.750702</v>
+      </c>
+      <c r="E25" t="n">
         <v>1</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>24.3206</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>16</v>
       </c>
     </row>
@@ -940,9 +1110,15 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
         <v>23.0014</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>21</v>
       </c>
     </row>
@@ -954,16 +1130,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12.729614</t>
+          <t>12.48941</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
+        <v>12.729614</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
         <v>19.4371</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>24</v>
       </c>
     </row>
@@ -973,18 +1155,22 @@
           <t>GASS</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>5.6517944</t>
-        </is>
+      <c r="B28" t="n">
+        <v>0</v>
       </c>
       <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5.6517944</v>
+      </c>
+      <c r="E28" t="n">
         <v>3</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>6.542200000000001</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>81</v>
       </c>
     </row>
@@ -1001,9 +1187,15 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>24.3519</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1020,9 +1212,15 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
         <v>30.1995</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>19</v>
       </c>
     </row>

--- a/TransactionHistory.xlsx
+++ b/TransactionHistory.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,32 +436,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Price paid 2025-02-22</t>
+          <t>Price paid 2025-02-23</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Quantity 2025-02-22</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Price paid 2025-02-15</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Quantity 2025-02-15</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Price paid 2025-02-14</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Quantity 2025-02-14</t>
+          <t>Quantity 2025-02-23</t>
         </is>
       </c>
     </row>
@@ -471,25 +451,11 @@
           <t>APT</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>5.401306</t>
-        </is>
+      <c r="B2" t="n">
+        <v>5.5993</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5.468811</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5.6074</v>
-      </c>
-      <c r="G2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -504,18 +470,6 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,25 +477,11 @@
           <t>AMPY</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5.3017273</t>
-        </is>
+      <c r="B4" t="n">
+        <v>6.4717</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5.2800903</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6.5376</v>
-      </c>
-      <c r="G4" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -550,25 +490,11 @@
           <t>CTRM</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>9.040024</t>
-        </is>
+      <c r="B5" t="n">
+        <v>3.64651</v>
       </c>
       <c r="C5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.6501873</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3.77771</v>
-      </c>
-      <c r="G5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6">
@@ -583,18 +509,6 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -603,21 +517,9 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>20.5765</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>20.855</v>
-      </c>
-      <c r="G7" t="n">
         <v>20</v>
       </c>
     </row>
@@ -627,25 +529,11 @@
           <t>CVLG</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>20.295593</t>
-        </is>
+      <c r="B8" t="n">
+        <v>23.0736</v>
       </c>
       <c r="C8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22.8421</v>
-      </c>
-      <c r="G8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -655,21 +543,9 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>11.7444</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>11.7444</v>
-      </c>
-      <c r="G9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -679,25 +555,11 @@
           <t>EBF</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>20.568878</t>
-        </is>
+      <c r="B10" t="n">
+        <v>21.4314</v>
       </c>
       <c r="C10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>21.3939</v>
-      </c>
-      <c r="G10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -707,21 +569,9 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>14.6113</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>14.5313</v>
-      </c>
-      <c r="G11" t="n">
         <v>23</v>
       </c>
     </row>
@@ -732,21 +582,9 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>16.8429</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>16.8429</v>
-      </c>
-      <c r="G12" t="n">
         <v>21</v>
       </c>
     </row>
@@ -756,25 +594,11 @@
           <t>FRD</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>10.241577</t>
-        </is>
+      <c r="B13" t="n">
+        <v>14.8054</v>
       </c>
       <c r="C13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>14.6853</v>
-      </c>
-      <c r="G13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -783,25 +607,11 @@
           <t>GILT</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>7.0509644</t>
-        </is>
+      <c r="B14" t="n">
+        <v>5.6968</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7.4802094</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5.5757</v>
-      </c>
-      <c r="G14" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -816,18 +626,6 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -835,25 +633,11 @@
           <t>KE</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>17.089874</t>
-        </is>
+      <c r="B16" t="n">
+        <v>23.054</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>23.3679</v>
-      </c>
-      <c r="G16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -862,25 +646,11 @@
           <t>LAKE</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13.7248535</t>
-        </is>
+      <c r="B17" t="n">
+        <v>18.1884</v>
       </c>
       <c r="C17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>17.7633</v>
-      </c>
-      <c r="G17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -889,25 +659,11 @@
           <t>LSEA</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>8.549904</t>
-        </is>
+      <c r="B18" t="n">
+        <v>8.306699999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>8.120445</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="G18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -916,25 +672,11 @@
           <t>MG</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>10.086609</t>
-        </is>
+      <c r="B19" t="n">
+        <v>8.2746</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>8.2293</v>
-      </c>
-      <c r="G19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -944,21 +686,9 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>32.3644</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>32.3644</v>
-      </c>
-      <c r="G20" t="n">
         <v>16</v>
       </c>
     </row>
@@ -968,25 +698,11 @@
           <t>NGS</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>27.650696</t>
-        </is>
+      <c r="B21" t="n">
+        <v>20.0207</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>25.769165</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>19.5252</v>
-      </c>
-      <c r="G21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
@@ -995,25 +711,11 @@
           <t>NSYS</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>10.000305</t>
-        </is>
+      <c r="B22" t="n">
+        <v>11.3379</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>10.340195</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>11.449</v>
-      </c>
-      <c r="G22" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -1022,25 +724,11 @@
           <t>PANL</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>5.2109375</t>
-        </is>
+      <c r="B23" t="n">
+        <v>5.4136</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5.4212</v>
-      </c>
-      <c r="G23" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24">
@@ -1049,25 +737,11 @@
           <t>PKOH</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>25.398895</t>
-        </is>
+      <c r="B24" t="n">
+        <v>23.8995</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>23.8281</v>
-      </c>
-      <c r="G24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1076,25 +750,11 @@
           <t>RGS</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>26.994904</t>
-        </is>
+      <c r="B25" t="n">
+        <v>23.9927</v>
       </c>
       <c r="C25" t="n">
-        <v>-2</v>
-      </c>
-      <c r="D25" t="n">
-        <v>24.750702</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>24.3206</v>
-      </c>
-      <c r="G25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1104,21 +764,9 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>23.0014</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>23.0014</v>
-      </c>
-      <c r="G26" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1128,25 +776,11 @@
           <t>SGA</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>12.48941</t>
-        </is>
+      <c r="B27" t="n">
+        <v>18.9119</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>12.729614</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>19.4371</v>
-      </c>
-      <c r="G27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -1156,22 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>6.5104</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>5.6517944</v>
-      </c>
-      <c r="E28" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" t="n">
-        <v>6.542200000000001</v>
-      </c>
-      <c r="G28" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29">
@@ -1181,21 +803,9 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>24.3519</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>24.3519</v>
-      </c>
-      <c r="G29" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1206,21 +816,9 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>30.1995</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>30.1995</v>
-      </c>
-      <c r="G30" t="n">
         <v>19</v>
       </c>
     </row>

--- a/TransactionHistory.xlsx
+++ b/TransactionHistory.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="I64C2tp+oHt8cTxkkCcEIWkKBrAkWMdQ+W3D+aHRf6k="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="sOynOXDFBsrH5otI0tEbGPOnV3J386lsuJYKg+XpV4U="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5914" uniqueCount="762">
   <si>
     <t>TransactionDate</t>
   </si>
@@ -2308,12 +2308,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="166" formatCode="m/d/yy"/>
+    <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -2328,6 +2329,11 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2344,7 +2350,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2368,6 +2374,13 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -66805,6 +66818,871 @@
       <c r="K2099" s="4"/>
       <c r="L2099" s="4"/>
     </row>
+    <row r="2100">
+      <c r="A2100" s="9">
+        <v>44690.0</v>
+      </c>
+      <c r="B2100" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2100" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2100" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2100" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F2100" s="11">
+        <f t="shared" ref="F2100:F2102" si="2">-E2100*G2100</f>
+        <v>-18.46</v>
+      </c>
+      <c r="G2100" s="10">
+        <v>18.46</v>
+      </c>
+      <c r="H2100" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="9">
+        <v>44664.0</v>
+      </c>
+      <c r="B2101" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2101" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2101" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2101" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F2101" s="11">
+        <f t="shared" si="2"/>
+        <v>-17.24</v>
+      </c>
+      <c r="G2101" s="10">
+        <v>17.24</v>
+      </c>
+      <c r="H2101" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="9">
+        <v>44664.0</v>
+      </c>
+      <c r="B2102" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2102" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2102" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2102" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="F2102" s="11">
+        <f t="shared" si="2"/>
+        <v>-17.33</v>
+      </c>
+      <c r="G2102" s="10">
+        <v>17.33</v>
+      </c>
+      <c r="H2102" s="10">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="9"/>
+      <c r="B2103" s="7"/>
+      <c r="C2103" s="4"/>
+      <c r="D2103" s="7"/>
+      <c r="E2103" s="10"/>
+      <c r="G2103" s="10"/>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="9"/>
+      <c r="B2104" s="7"/>
+      <c r="C2104" s="4"/>
+      <c r="D2104" s="7"/>
+      <c r="E2104" s="10"/>
+      <c r="G2104" s="10"/>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="9"/>
+      <c r="B2105" s="7"/>
+      <c r="C2105" s="4"/>
+      <c r="D2105" s="7"/>
+      <c r="E2105" s="10"/>
+      <c r="G2105" s="10"/>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="9"/>
+      <c r="B2106" s="7"/>
+      <c r="C2106" s="4"/>
+      <c r="D2106" s="7"/>
+      <c r="E2106" s="10"/>
+      <c r="G2106" s="10"/>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="9"/>
+      <c r="B2107" s="7"/>
+      <c r="C2107" s="4"/>
+      <c r="D2107" s="7"/>
+      <c r="E2107" s="10"/>
+      <c r="G2107" s="10"/>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="9"/>
+      <c r="B2108" s="7"/>
+      <c r="C2108" s="4"/>
+      <c r="D2108" s="7"/>
+      <c r="E2108" s="10"/>
+      <c r="G2108" s="10"/>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="9"/>
+      <c r="B2109" s="7"/>
+      <c r="C2109" s="4"/>
+      <c r="D2109" s="7"/>
+      <c r="E2109" s="10"/>
+      <c r="G2109" s="10"/>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="9"/>
+      <c r="B2110" s="7"/>
+      <c r="C2110" s="4"/>
+      <c r="D2110" s="7"/>
+      <c r="E2110" s="10"/>
+      <c r="G2110" s="10"/>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="9"/>
+      <c r="B2111" s="7"/>
+      <c r="C2111" s="4"/>
+      <c r="D2111" s="7"/>
+      <c r="E2111" s="10"/>
+      <c r="G2111" s="10"/>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="9"/>
+      <c r="B2112" s="7"/>
+      <c r="C2112" s="4"/>
+      <c r="D2112" s="7"/>
+      <c r="E2112" s="10"/>
+      <c r="G2112" s="10"/>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="9"/>
+      <c r="B2113" s="7"/>
+      <c r="C2113" s="4"/>
+      <c r="D2113" s="7"/>
+      <c r="E2113" s="10"/>
+      <c r="G2113" s="10"/>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="9"/>
+      <c r="B2114" s="7"/>
+      <c r="C2114" s="4"/>
+      <c r="D2114" s="7"/>
+      <c r="E2114" s="10"/>
+      <c r="G2114" s="10"/>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="9"/>
+      <c r="B2115" s="7"/>
+      <c r="C2115" s="4"/>
+      <c r="D2115" s="7"/>
+      <c r="E2115" s="10"/>
+      <c r="G2115" s="10"/>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="9"/>
+      <c r="B2116" s="7"/>
+      <c r="C2116" s="4"/>
+      <c r="D2116" s="7"/>
+      <c r="E2116" s="10"/>
+      <c r="G2116" s="10"/>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="9"/>
+      <c r="B2117" s="7"/>
+      <c r="C2117" s="4"/>
+      <c r="D2117" s="7"/>
+      <c r="E2117" s="10"/>
+      <c r="G2117" s="10"/>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="9"/>
+      <c r="B2118" s="7"/>
+      <c r="C2118" s="4"/>
+      <c r="D2118" s="7"/>
+      <c r="E2118" s="10"/>
+      <c r="G2118" s="10"/>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="9"/>
+      <c r="B2119" s="7"/>
+      <c r="C2119" s="4"/>
+      <c r="D2119" s="7"/>
+      <c r="E2119" s="10"/>
+      <c r="G2119" s="10"/>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="9"/>
+      <c r="B2120" s="7"/>
+      <c r="C2120" s="4"/>
+      <c r="D2120" s="7"/>
+      <c r="E2120" s="10"/>
+      <c r="G2120" s="10"/>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="9"/>
+      <c r="B2121" s="7"/>
+      <c r="C2121" s="4"/>
+      <c r="D2121" s="7"/>
+      <c r="E2121" s="10"/>
+      <c r="G2121" s="10"/>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="9"/>
+      <c r="B2122" s="7"/>
+      <c r="C2122" s="4"/>
+      <c r="D2122" s="7"/>
+      <c r="E2122" s="10"/>
+      <c r="G2122" s="10"/>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="9"/>
+      <c r="B2123" s="7"/>
+      <c r="C2123" s="4"/>
+      <c r="D2123" s="7"/>
+      <c r="E2123" s="10"/>
+      <c r="G2123" s="10"/>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="9"/>
+      <c r="B2124" s="7"/>
+      <c r="C2124" s="4"/>
+      <c r="D2124" s="7"/>
+      <c r="E2124" s="10"/>
+      <c r="G2124" s="10"/>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="9"/>
+      <c r="B2125" s="7"/>
+      <c r="C2125" s="4"/>
+      <c r="D2125" s="7"/>
+      <c r="E2125" s="10"/>
+      <c r="G2125" s="10"/>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="9"/>
+      <c r="B2126" s="7"/>
+      <c r="C2126" s="4"/>
+      <c r="D2126" s="7"/>
+      <c r="E2126" s="10"/>
+      <c r="G2126" s="10"/>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="9"/>
+      <c r="B2127" s="7"/>
+      <c r="C2127" s="4"/>
+      <c r="D2127" s="7"/>
+      <c r="E2127" s="10"/>
+      <c r="G2127" s="10"/>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="9"/>
+      <c r="B2128" s="7"/>
+      <c r="C2128" s="4"/>
+      <c r="D2128" s="7"/>
+      <c r="E2128" s="10"/>
+      <c r="G2128" s="10"/>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="9"/>
+      <c r="B2129" s="7"/>
+      <c r="C2129" s="4"/>
+      <c r="D2129" s="7"/>
+      <c r="E2129" s="10"/>
+      <c r="G2129" s="10"/>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="9"/>
+      <c r="B2130" s="7"/>
+      <c r="C2130" s="4"/>
+      <c r="D2130" s="7"/>
+      <c r="E2130" s="10"/>
+      <c r="G2130" s="10"/>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="9"/>
+      <c r="B2131" s="7"/>
+      <c r="C2131" s="4"/>
+      <c r="D2131" s="7"/>
+      <c r="E2131" s="10"/>
+      <c r="G2131" s="10"/>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="9"/>
+      <c r="B2132" s="7"/>
+      <c r="C2132" s="4"/>
+      <c r="D2132" s="7"/>
+      <c r="E2132" s="10"/>
+      <c r="G2132" s="10"/>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="9"/>
+      <c r="B2133" s="7"/>
+      <c r="C2133" s="4"/>
+      <c r="D2133" s="7"/>
+      <c r="E2133" s="10"/>
+      <c r="G2133" s="10"/>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="9"/>
+      <c r="B2134" s="7"/>
+      <c r="C2134" s="4"/>
+      <c r="D2134" s="7"/>
+      <c r="E2134" s="10"/>
+      <c r="G2134" s="10"/>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="9"/>
+      <c r="B2135" s="7"/>
+      <c r="C2135" s="4"/>
+      <c r="D2135" s="7"/>
+      <c r="E2135" s="10"/>
+      <c r="G2135" s="10"/>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="9"/>
+      <c r="B2136" s="7"/>
+      <c r="C2136" s="4"/>
+      <c r="D2136" s="7"/>
+      <c r="E2136" s="10"/>
+      <c r="G2136" s="10"/>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="9"/>
+      <c r="B2137" s="7"/>
+      <c r="C2137" s="4"/>
+      <c r="D2137" s="7"/>
+      <c r="E2137" s="10"/>
+      <c r="G2137" s="10"/>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="9"/>
+      <c r="B2138" s="7"/>
+      <c r="C2138" s="4"/>
+      <c r="D2138" s="7"/>
+      <c r="E2138" s="10"/>
+      <c r="G2138" s="10"/>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="9"/>
+      <c r="B2139" s="7"/>
+      <c r="C2139" s="4"/>
+      <c r="D2139" s="7"/>
+      <c r="E2139" s="10"/>
+      <c r="G2139" s="10"/>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="9"/>
+      <c r="B2140" s="7"/>
+      <c r="C2140" s="4"/>
+      <c r="D2140" s="7"/>
+      <c r="E2140" s="10"/>
+      <c r="G2140" s="10"/>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="9"/>
+      <c r="B2141" s="7"/>
+      <c r="C2141" s="4"/>
+      <c r="D2141" s="7"/>
+      <c r="E2141" s="10"/>
+      <c r="G2141" s="10"/>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="9"/>
+      <c r="B2142" s="7"/>
+      <c r="C2142" s="4"/>
+      <c r="D2142" s="7"/>
+      <c r="E2142" s="10"/>
+      <c r="G2142" s="10"/>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="9"/>
+      <c r="B2143" s="7"/>
+      <c r="C2143" s="4"/>
+      <c r="D2143" s="7"/>
+      <c r="E2143" s="10"/>
+      <c r="G2143" s="10"/>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="9"/>
+      <c r="B2144" s="7"/>
+      <c r="C2144" s="4"/>
+      <c r="D2144" s="7"/>
+      <c r="E2144" s="10"/>
+      <c r="G2144" s="10"/>
+    </row>
+    <row r="2145">
+      <c r="A2145" s="9"/>
+      <c r="B2145" s="7"/>
+      <c r="C2145" s="4"/>
+      <c r="D2145" s="7"/>
+      <c r="E2145" s="10"/>
+      <c r="G2145" s="10"/>
+    </row>
+    <row r="2146">
+      <c r="A2146" s="9"/>
+      <c r="B2146" s="7"/>
+      <c r="C2146" s="4"/>
+      <c r="D2146" s="7"/>
+      <c r="E2146" s="10"/>
+      <c r="G2146" s="10"/>
+    </row>
+    <row r="2147">
+      <c r="A2147" s="9"/>
+      <c r="B2147" s="7"/>
+      <c r="C2147" s="4"/>
+      <c r="D2147" s="7"/>
+      <c r="E2147" s="10"/>
+      <c r="G2147" s="10"/>
+    </row>
+    <row r="2148">
+      <c r="A2148" s="9"/>
+      <c r="B2148" s="7"/>
+      <c r="C2148" s="4"/>
+      <c r="D2148" s="7"/>
+      <c r="E2148" s="10"/>
+      <c r="G2148" s="10"/>
+    </row>
+    <row r="2149">
+      <c r="A2149" s="9"/>
+      <c r="B2149" s="7"/>
+      <c r="C2149" s="4"/>
+      <c r="D2149" s="7"/>
+      <c r="E2149" s="10"/>
+      <c r="G2149" s="10"/>
+    </row>
+    <row r="2150">
+      <c r="A2150" s="9"/>
+      <c r="B2150" s="7"/>
+      <c r="C2150" s="4"/>
+      <c r="D2150" s="7"/>
+      <c r="E2150" s="10"/>
+      <c r="G2150" s="10"/>
+    </row>
+    <row r="2151">
+      <c r="A2151" s="9"/>
+      <c r="B2151" s="7"/>
+      <c r="C2151" s="4"/>
+      <c r="D2151" s="7"/>
+      <c r="E2151" s="10"/>
+      <c r="G2151" s="10"/>
+    </row>
+    <row r="2152">
+      <c r="A2152" s="9"/>
+      <c r="B2152" s="7"/>
+      <c r="C2152" s="4"/>
+      <c r="D2152" s="7"/>
+      <c r="E2152" s="10"/>
+      <c r="G2152" s="10"/>
+    </row>
+    <row r="2153">
+      <c r="A2153" s="9"/>
+      <c r="B2153" s="7"/>
+      <c r="C2153" s="4"/>
+      <c r="D2153" s="7"/>
+      <c r="E2153" s="10"/>
+      <c r="G2153" s="10"/>
+    </row>
+    <row r="2154">
+      <c r="A2154" s="9"/>
+      <c r="B2154" s="7"/>
+      <c r="C2154" s="4"/>
+      <c r="D2154" s="7"/>
+      <c r="E2154" s="10"/>
+      <c r="G2154" s="10"/>
+    </row>
+    <row r="2155">
+      <c r="A2155" s="9"/>
+      <c r="B2155" s="7"/>
+      <c r="C2155" s="4"/>
+      <c r="D2155" s="7"/>
+      <c r="E2155" s="10"/>
+      <c r="G2155" s="10"/>
+    </row>
+    <row r="2156">
+      <c r="A2156" s="9"/>
+      <c r="B2156" s="7"/>
+      <c r="C2156" s="4"/>
+      <c r="D2156" s="7"/>
+      <c r="E2156" s="10"/>
+      <c r="G2156" s="10"/>
+    </row>
+    <row r="2157">
+      <c r="A2157" s="9"/>
+      <c r="B2157" s="7"/>
+      <c r="C2157" s="4"/>
+      <c r="D2157" s="7"/>
+      <c r="E2157" s="10"/>
+      <c r="G2157" s="10"/>
+    </row>
+    <row r="2158">
+      <c r="A2158" s="9"/>
+      <c r="B2158" s="7"/>
+      <c r="C2158" s="4"/>
+      <c r="D2158" s="7"/>
+      <c r="E2158" s="10"/>
+      <c r="G2158" s="10"/>
+    </row>
+    <row r="2159">
+      <c r="A2159" s="9"/>
+      <c r="B2159" s="7"/>
+      <c r="C2159" s="4"/>
+      <c r="D2159" s="7"/>
+      <c r="E2159" s="10"/>
+      <c r="G2159" s="10"/>
+    </row>
+    <row r="2160">
+      <c r="A2160" s="9"/>
+      <c r="B2160" s="7"/>
+      <c r="C2160" s="4"/>
+      <c r="D2160" s="7"/>
+      <c r="E2160" s="10"/>
+      <c r="G2160" s="10"/>
+    </row>
+    <row r="2161">
+      <c r="A2161" s="9"/>
+      <c r="B2161" s="7"/>
+      <c r="C2161" s="4"/>
+      <c r="D2161" s="7"/>
+      <c r="E2161" s="10"/>
+      <c r="G2161" s="10"/>
+    </row>
+    <row r="2162">
+      <c r="A2162" s="9"/>
+      <c r="B2162" s="7"/>
+      <c r="C2162" s="4"/>
+      <c r="D2162" s="7"/>
+      <c r="E2162" s="10"/>
+      <c r="G2162" s="10"/>
+    </row>
+    <row r="2163">
+      <c r="A2163" s="9"/>
+      <c r="B2163" s="7"/>
+      <c r="C2163" s="4"/>
+      <c r="D2163" s="7"/>
+      <c r="E2163" s="10"/>
+      <c r="G2163" s="10"/>
+    </row>
+    <row r="2164">
+      <c r="A2164" s="9"/>
+      <c r="B2164" s="7"/>
+      <c r="C2164" s="4"/>
+      <c r="D2164" s="7"/>
+      <c r="E2164" s="10"/>
+      <c r="G2164" s="10"/>
+    </row>
+    <row r="2165">
+      <c r="A2165" s="9"/>
+      <c r="B2165" s="7"/>
+      <c r="C2165" s="4"/>
+      <c r="D2165" s="7"/>
+      <c r="E2165" s="10"/>
+      <c r="G2165" s="10"/>
+    </row>
+    <row r="2166">
+      <c r="A2166" s="9"/>
+      <c r="B2166" s="7"/>
+      <c r="C2166" s="4"/>
+      <c r="D2166" s="7"/>
+      <c r="E2166" s="10"/>
+      <c r="G2166" s="10"/>
+    </row>
+    <row r="2167">
+      <c r="A2167" s="9"/>
+      <c r="B2167" s="7"/>
+      <c r="C2167" s="4"/>
+      <c r="D2167" s="7"/>
+      <c r="E2167" s="10"/>
+      <c r="G2167" s="10"/>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="9"/>
+      <c r="B2168" s="7"/>
+      <c r="C2168" s="4"/>
+      <c r="D2168" s="7"/>
+      <c r="E2168" s="10"/>
+      <c r="G2168" s="10"/>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="9"/>
+      <c r="B2169" s="7"/>
+      <c r="C2169" s="4"/>
+      <c r="D2169" s="7"/>
+      <c r="E2169" s="10"/>
+      <c r="G2169" s="10"/>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="9"/>
+      <c r="B2170" s="7"/>
+      <c r="C2170" s="4"/>
+      <c r="D2170" s="7"/>
+      <c r="E2170" s="10"/>
+      <c r="G2170" s="10"/>
+    </row>
+    <row r="2171">
+      <c r="A2171" s="9"/>
+      <c r="B2171" s="7"/>
+      <c r="C2171" s="4"/>
+      <c r="D2171" s="7"/>
+      <c r="E2171" s="10"/>
+      <c r="G2171" s="10"/>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="9"/>
+      <c r="B2172" s="7"/>
+      <c r="C2172" s="4"/>
+      <c r="D2172" s="7"/>
+      <c r="E2172" s="10"/>
+      <c r="G2172" s="10"/>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="9"/>
+      <c r="B2173" s="7"/>
+      <c r="C2173" s="4"/>
+      <c r="D2173" s="7"/>
+      <c r="E2173" s="10"/>
+      <c r="G2173" s="10"/>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="9"/>
+      <c r="B2174" s="7"/>
+      <c r="C2174" s="4"/>
+      <c r="D2174" s="7"/>
+      <c r="E2174" s="10"/>
+      <c r="G2174" s="10"/>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="9"/>
+      <c r="B2175" s="7"/>
+      <c r="C2175" s="4"/>
+      <c r="D2175" s="7"/>
+      <c r="E2175" s="10"/>
+      <c r="G2175" s="10"/>
+    </row>
+    <row r="2176">
+      <c r="A2176" s="9"/>
+      <c r="B2176" s="7"/>
+      <c r="C2176" s="4"/>
+      <c r="D2176" s="7"/>
+      <c r="E2176" s="10"/>
+      <c r="G2176" s="10"/>
+    </row>
+    <row r="2177">
+      <c r="A2177" s="9"/>
+      <c r="B2177" s="7"/>
+      <c r="C2177" s="4"/>
+      <c r="D2177" s="7"/>
+      <c r="E2177" s="10"/>
+      <c r="G2177" s="10"/>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="9"/>
+      <c r="B2178" s="7"/>
+      <c r="C2178" s="4"/>
+      <c r="D2178" s="7"/>
+      <c r="E2178" s="10"/>
+      <c r="G2178" s="10"/>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="9"/>
+      <c r="B2179" s="7"/>
+      <c r="C2179" s="4"/>
+      <c r="D2179" s="7"/>
+      <c r="E2179" s="10"/>
+      <c r="G2179" s="10"/>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="9"/>
+      <c r="B2180" s="7"/>
+      <c r="C2180" s="4"/>
+      <c r="D2180" s="7"/>
+      <c r="E2180" s="10"/>
+      <c r="G2180" s="10"/>
+    </row>
+    <row r="2181">
+      <c r="A2181" s="9"/>
+      <c r="B2181" s="7"/>
+      <c r="C2181" s="4"/>
+      <c r="D2181" s="7"/>
+      <c r="E2181" s="10"/>
+      <c r="G2181" s="10"/>
+    </row>
+    <row r="2182">
+      <c r="A2182" s="9"/>
+      <c r="B2182" s="7"/>
+      <c r="C2182" s="4"/>
+      <c r="D2182" s="7"/>
+      <c r="E2182" s="10"/>
+      <c r="G2182" s="10"/>
+    </row>
+    <row r="2183">
+      <c r="A2183" s="9"/>
+      <c r="B2183" s="7"/>
+      <c r="C2183" s="4"/>
+      <c r="D2183" s="7"/>
+      <c r="E2183" s="10"/>
+      <c r="G2183" s="10"/>
+    </row>
+    <row r="2184">
+      <c r="A2184" s="9"/>
+      <c r="B2184" s="7"/>
+      <c r="C2184" s="4"/>
+      <c r="D2184" s="7"/>
+      <c r="E2184" s="10"/>
+      <c r="G2184" s="10"/>
+    </row>
+    <row r="2185">
+      <c r="A2185" s="9"/>
+      <c r="B2185" s="7"/>
+      <c r="C2185" s="4"/>
+      <c r="D2185" s="7"/>
+      <c r="E2185" s="10"/>
+      <c r="G2185" s="10"/>
+    </row>
+    <row r="2186">
+      <c r="A2186" s="9"/>
+      <c r="B2186" s="7"/>
+      <c r="C2186" s="4"/>
+      <c r="D2186" s="7"/>
+      <c r="E2186" s="10"/>
+      <c r="G2186" s="10"/>
+    </row>
+    <row r="2187">
+      <c r="A2187" s="9"/>
+      <c r="B2187" s="7"/>
+      <c r="C2187" s="4"/>
+      <c r="D2187" s="7"/>
+      <c r="E2187" s="10"/>
+      <c r="G2187" s="10"/>
+    </row>
+    <row r="2188">
+      <c r="A2188" s="9"/>
+      <c r="B2188" s="7"/>
+      <c r="C2188" s="4"/>
+      <c r="D2188" s="7"/>
+      <c r="E2188" s="10"/>
+      <c r="G2188" s="10"/>
+    </row>
+    <row r="2189">
+      <c r="A2189" s="9"/>
+      <c r="B2189" s="7"/>
+      <c r="C2189" s="4"/>
+      <c r="D2189" s="7"/>
+      <c r="E2189" s="10"/>
+      <c r="G2189" s="10"/>
+    </row>
+    <row r="2190">
+      <c r="A2190" s="9"/>
+      <c r="B2190" s="7"/>
+      <c r="C2190" s="4"/>
+      <c r="D2190" s="7"/>
+      <c r="E2190" s="10"/>
+      <c r="G2190" s="10"/>
+    </row>
+    <row r="2191">
+      <c r="A2191" s="9"/>
+      <c r="B2191" s="7"/>
+      <c r="C2191" s="4"/>
+      <c r="D2191" s="7"/>
+      <c r="E2191" s="10"/>
+      <c r="G2191" s="10"/>
+    </row>
+    <row r="2192">
+      <c r="A2192" s="9"/>
+      <c r="B2192" s="7"/>
+      <c r="C2192" s="4"/>
+      <c r="D2192" s="7"/>
+      <c r="E2192" s="10"/>
+      <c r="G2192" s="10"/>
+    </row>
+    <row r="2193">
+      <c r="A2193" s="9"/>
+      <c r="B2193" s="7"/>
+      <c r="C2193" s="4"/>
+      <c r="D2193" s="7"/>
+      <c r="E2193" s="10"/>
+      <c r="G2193" s="10"/>
+    </row>
+    <row r="2194">
+      <c r="A2194" s="9"/>
+      <c r="B2194" s="7"/>
+      <c r="C2194" s="4"/>
+      <c r="D2194" s="7"/>
+      <c r="E2194" s="10"/>
+      <c r="G2194" s="10"/>
+    </row>
+    <row r="2195">
+      <c r="A2195" s="9"/>
+      <c r="B2195" s="7"/>
+      <c r="C2195" s="4"/>
+      <c r="D2195" s="7"/>
+      <c r="E2195" s="10"/>
+      <c r="G2195" s="10"/>
+    </row>
+    <row r="2196">
+      <c r="A2196" s="9"/>
+      <c r="B2196" s="7"/>
+      <c r="C2196" s="4"/>
+      <c r="D2196" s="7"/>
+      <c r="E2196" s="10"/>
+      <c r="G2196" s="10"/>
+    </row>
+    <row r="2197">
+      <c r="A2197" s="9"/>
+      <c r="B2197" s="7"/>
+      <c r="C2197" s="4"/>
+      <c r="D2197" s="7"/>
+      <c r="E2197" s="10"/>
+      <c r="G2197" s="10"/>
+    </row>
+    <row r="2198">
+      <c r="A2198" s="9"/>
+      <c r="B2198" s="7"/>
+      <c r="C2198" s="4"/>
+      <c r="D2198" s="7"/>
+      <c r="E2198" s="10"/>
+      <c r="G2198" s="10"/>
+    </row>
+    <row r="2199">
+      <c r="A2199" s="9"/>
+      <c r="B2199" s="7"/>
+      <c r="C2199" s="4"/>
+      <c r="D2199" s="7"/>
+      <c r="E2199" s="10"/>
+      <c r="G2199" s="10"/>
+    </row>
+    <row r="2200">
+      <c r="A2200" s="9"/>
+      <c r="B2200" s="7"/>
+      <c r="C2200" s="4"/>
+      <c r="D2200" s="7"/>
+      <c r="E2200" s="10"/>
+      <c r="G2200" s="10"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/TransactionHistory.xlsx
+++ b/TransactionHistory.xlsx
@@ -62864,19 +62864,15 @@
       <c r="C1575" s="2" t="n">
         <v>45243</v>
       </c>
-      <c r="D1575" t="inlineStr">
+      <c r="D1575" t="inlineStr"/>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>TITAN MACHINERY INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1575" t="inlineStr">
         <is>
           <t>TITN</t>
-        </is>
-      </c>
-      <c r="E1575" t="inlineStr">
-        <is>
-          <t>TITAN MACHINERY INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1575" t="inlineStr">
-        <is>
-          <t>EQ</t>
         </is>
       </c>
       <c r="G1575" t="inlineStr"/>
@@ -62903,17 +62899,17 @@
       <c r="C1576" s="2" t="n">
         <v>45243</v>
       </c>
-      <c r="D1576" t="inlineStr">
+      <c r="D1576" t="inlineStr"/>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>HOOKER FURNISHINGS CORPORATION UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1576" t="inlineStr">
         <is>
           <t>HOFT</t>
         </is>
       </c>
-      <c r="E1576" t="inlineStr">
-        <is>
-          <t>HOOKER FURNISHINGS CORPORATION UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1576" t="inlineStr"/>
       <c r="G1576" t="inlineStr"/>
       <c r="H1576" t="n">
         <v>1</v>
@@ -62938,17 +62934,17 @@
       <c r="C1577" s="2" t="n">
         <v>45243</v>
       </c>
-      <c r="D1577" t="inlineStr">
+      <c r="D1577" t="inlineStr"/>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC COM UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1577" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1577" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC COM UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1577" t="inlineStr"/>
       <c r="G1577" t="inlineStr"/>
       <c r="H1577" t="n">
         <v>-3</v>
@@ -62973,17 +62969,17 @@
       <c r="C1578" s="2" t="n">
         <v>45243</v>
       </c>
-      <c r="D1578" t="inlineStr">
+      <c r="D1578" t="inlineStr"/>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1578" t="inlineStr">
         <is>
           <t>HURC</t>
         </is>
       </c>
-      <c r="E1578" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1578" t="inlineStr"/>
       <c r="G1578" t="inlineStr"/>
       <c r="H1578" t="n">
         <v>1</v>
@@ -63008,17 +63004,17 @@
       <c r="C1579" s="2" t="n">
         <v>45243</v>
       </c>
-      <c r="D1579" t="inlineStr">
+      <c r="D1579" t="inlineStr"/>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1579" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1579" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1579" t="inlineStr"/>
       <c r="G1579" t="inlineStr"/>
       <c r="H1579" t="n">
         <v>1</v>
@@ -63043,17 +63039,17 @@
       <c r="C1580" s="2" t="n">
         <v>45243</v>
       </c>
-      <c r="D1580" t="inlineStr">
+      <c r="D1580" t="inlineStr"/>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>NACCO INDUSTRIES A UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1580" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E1580" t="inlineStr">
-        <is>
-          <t>NACCO INDUSTRIES A UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1580" t="inlineStr"/>
       <c r="G1580" t="inlineStr"/>
       <c r="H1580" t="n">
         <v>1</v>
@@ -63078,17 +63074,17 @@
       <c r="C1581" s="2" t="n">
         <v>45243</v>
       </c>
-      <c r="D1581" t="inlineStr">
+      <c r="D1581" t="inlineStr"/>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>VISHAY PRECISION GROUP INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1581" t="inlineStr">
         <is>
           <t>VPG</t>
         </is>
       </c>
-      <c r="E1581" t="inlineStr">
-        <is>
-          <t>VISHAY PRECISION GROUP INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1581" t="inlineStr"/>
       <c r="G1581" t="inlineStr"/>
       <c r="H1581" t="n">
         <v>1</v>
@@ -63113,17 +63109,17 @@
       <c r="C1582" s="2" t="n">
         <v>45243</v>
       </c>
-      <c r="D1582" t="inlineStr">
+      <c r="D1582" t="inlineStr"/>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>COVENANT TRANSN GROUP INC CL A UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1582" t="inlineStr">
         <is>
           <t>CVLG</t>
         </is>
       </c>
-      <c r="E1582" t="inlineStr">
-        <is>
-          <t>COVENANT TRANSN GROUP INC CL A UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1582" t="inlineStr"/>
       <c r="G1582" t="inlineStr"/>
       <c r="H1582" t="n">
         <v>1</v>
@@ -63148,17 +63144,17 @@
       <c r="C1583" s="2" t="n">
         <v>45243</v>
       </c>
-      <c r="D1583" t="inlineStr">
+      <c r="D1583" t="inlineStr"/>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1583" t="inlineStr">
         <is>
           <t>SGMA</t>
         </is>
       </c>
-      <c r="E1583" t="inlineStr">
-        <is>
-          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1583" t="inlineStr"/>
       <c r="G1583" t="inlineStr"/>
       <c r="H1583" t="n">
         <v>4</v>
@@ -63183,17 +63179,17 @@
       <c r="C1584" s="2" t="n">
         <v>45243</v>
       </c>
-      <c r="D1584" t="inlineStr">
+      <c r="D1584" t="inlineStr"/>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>KEY TRONIC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1584" t="inlineStr">
         <is>
           <t>KTCC</t>
         </is>
       </c>
-      <c r="E1584" t="inlineStr">
-        <is>
-          <t>KEY TRONIC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1584" t="inlineStr"/>
       <c r="G1584" t="inlineStr"/>
       <c r="H1584" t="n">
         <v>1</v>
@@ -63218,17 +63214,17 @@
       <c r="C1585" s="2" t="n">
         <v>45243</v>
       </c>
-      <c r="D1585" t="inlineStr">
+      <c r="D1585" t="inlineStr"/>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1585" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1585" t="inlineStr">
-        <is>
-          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1585" t="inlineStr"/>
       <c r="G1585" t="inlineStr"/>
       <c r="H1585" t="n">
         <v>2</v>
@@ -63253,17 +63249,17 @@
       <c r="C1586" s="2" t="n">
         <v>45240</v>
       </c>
-      <c r="D1586" t="inlineStr">
+      <c r="D1586" t="inlineStr"/>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC REC 11/10/23 PAY 11/10/23 RATE 0.00000000 QTY 0.00000000</t>
+        </is>
+      </c>
+      <c r="F1586" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1586" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC REC 11/10/23 PAY 11/10/23 RATE 0.00000000 QTY 0.00000000</t>
-        </is>
-      </c>
-      <c r="F1586" t="inlineStr"/>
       <c r="G1586" t="inlineStr"/>
       <c r="H1586" t="n">
         <v>0</v>
@@ -63327,19 +63323,15 @@
       <c r="C1588" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1588" t="inlineStr">
+      <c r="D1588" t="inlineStr"/>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>BASSETT FURNITURE UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1588" t="inlineStr">
         <is>
           <t>BSET</t>
-        </is>
-      </c>
-      <c r="E1588" t="inlineStr">
-        <is>
-          <t>BASSETT FURNITURE UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1588" t="inlineStr">
-        <is>
-          <t>EQ</t>
         </is>
       </c>
       <c r="G1588" t="inlineStr"/>
@@ -63366,17 +63358,17 @@
       <c r="C1589" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1589" t="inlineStr">
+      <c r="D1589" t="inlineStr"/>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1589" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1589" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1589" t="inlineStr"/>
       <c r="G1589" t="inlineStr"/>
       <c r="H1589" t="n">
         <v>2</v>
@@ -63401,17 +63393,17 @@
       <c r="C1590" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1590" t="inlineStr">
+      <c r="D1590" t="inlineStr"/>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>FONAR CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1590" t="inlineStr">
         <is>
           <t>FONR</t>
         </is>
       </c>
-      <c r="E1590" t="inlineStr">
-        <is>
-          <t>FONAR CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1590" t="inlineStr"/>
       <c r="G1590" t="inlineStr"/>
       <c r="H1590" t="n">
         <v>1</v>
@@ -63436,17 +63428,17 @@
       <c r="C1591" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1591" t="inlineStr">
+      <c r="D1591" t="inlineStr"/>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>KEY TRONIC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1591" t="inlineStr">
         <is>
           <t>KTCC</t>
         </is>
       </c>
-      <c r="E1591" t="inlineStr">
-        <is>
-          <t>KEY TRONIC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1591" t="inlineStr"/>
       <c r="G1591" t="inlineStr"/>
       <c r="H1591" t="n">
         <v>2</v>
@@ -63471,17 +63463,17 @@
       <c r="C1592" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1592" t="inlineStr">
+      <c r="D1592" t="inlineStr"/>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>DUCOMMUN INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1592" t="inlineStr">
         <is>
           <t>DCO</t>
         </is>
       </c>
-      <c r="E1592" t="inlineStr">
-        <is>
-          <t>DUCOMMUN INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1592" t="inlineStr"/>
       <c r="G1592" t="inlineStr"/>
       <c r="H1592" t="n">
         <v>1</v>
@@ -63506,17 +63498,17 @@
       <c r="C1593" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1593" t="inlineStr">
+      <c r="D1593" t="inlineStr"/>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>CLARUS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1593" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1593" t="inlineStr">
-        <is>
-          <t>CLARUS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1593" t="inlineStr"/>
       <c r="G1593" t="inlineStr"/>
       <c r="H1593" t="n">
         <v>1</v>
@@ -63541,17 +63533,17 @@
       <c r="C1594" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1594" t="inlineStr">
+      <c r="D1594" t="inlineStr"/>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1594" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1594" t="inlineStr">
-        <is>
-          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1594" t="inlineStr"/>
       <c r="G1594" t="inlineStr"/>
       <c r="H1594" t="n">
         <v>1</v>
@@ -63576,17 +63568,17 @@
       <c r="C1595" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1595" t="inlineStr">
+      <c r="D1595" t="inlineStr"/>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1595" t="inlineStr">
         <is>
           <t>PKOH</t>
         </is>
       </c>
-      <c r="E1595" t="inlineStr">
-        <is>
-          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1595" t="inlineStr"/>
       <c r="G1595" t="inlineStr"/>
       <c r="H1595" t="n">
         <v>1</v>
@@ -63611,17 +63603,17 @@
       <c r="C1596" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1596" t="inlineStr">
+      <c r="D1596" t="inlineStr"/>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECH INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1596" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1596" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECH INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1596" t="inlineStr"/>
       <c r="G1596" t="inlineStr"/>
       <c r="H1596" t="n">
         <v>1</v>
@@ -63646,17 +63638,17 @@
       <c r="C1597" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1597" t="inlineStr">
+      <c r="D1597" t="inlineStr"/>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1597" t="inlineStr">
         <is>
           <t>SGMA</t>
         </is>
       </c>
-      <c r="E1597" t="inlineStr">
-        <is>
-          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1597" t="inlineStr"/>
       <c r="G1597" t="inlineStr"/>
       <c r="H1597" t="n">
         <v>1</v>
@@ -63681,17 +63673,17 @@
       <c r="C1598" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1598" t="inlineStr">
+      <c r="D1598" t="inlineStr"/>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1598" t="inlineStr">
         <is>
           <t>SGMA</t>
         </is>
       </c>
-      <c r="E1598" t="inlineStr">
-        <is>
-          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1598" t="inlineStr"/>
       <c r="G1598" t="inlineStr"/>
       <c r="H1598" t="n">
         <v>5</v>
@@ -63716,17 +63708,17 @@
       <c r="C1599" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1599" t="inlineStr">
+      <c r="D1599" t="inlineStr"/>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC COM UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1599" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1599" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC COM UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1599" t="inlineStr"/>
       <c r="G1599" t="inlineStr"/>
       <c r="H1599" t="n">
         <v>2</v>
@@ -63751,17 +63743,17 @@
       <c r="C1600" s="2" t="n">
         <v>45236</v>
       </c>
-      <c r="D1600" t="inlineStr">
+      <c r="D1600" t="inlineStr"/>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1600" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1600" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1600" t="inlineStr"/>
       <c r="G1600" t="inlineStr"/>
       <c r="H1600" t="n">
         <v>1</v>
@@ -63864,19 +63856,15 @@
       <c r="C1603" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="D1603" t="inlineStr">
+      <c r="D1603" t="inlineStr"/>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>BASSETT FURNITURE UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1603" t="inlineStr">
         <is>
           <t>BSET</t>
-        </is>
-      </c>
-      <c r="E1603" t="inlineStr">
-        <is>
-          <t>BASSETT FURNITURE UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1603" t="inlineStr">
-        <is>
-          <t>EQ</t>
         </is>
       </c>
       <c r="G1603" t="inlineStr"/>
@@ -63903,17 +63891,17 @@
       <c r="C1604" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="D1604" t="inlineStr">
+      <c r="D1604" t="inlineStr"/>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>HOOKER FURNISHINGS CORPORATION UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1604" t="inlineStr">
         <is>
           <t>HOFT</t>
         </is>
       </c>
-      <c r="E1604" t="inlineStr">
-        <is>
-          <t>HOOKER FURNISHINGS CORPORATION UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1604" t="inlineStr"/>
       <c r="G1604" t="inlineStr"/>
       <c r="H1604" t="n">
         <v>1</v>
@@ -63938,17 +63926,17 @@
       <c r="C1605" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="D1605" t="inlineStr">
+      <c r="D1605" t="inlineStr"/>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1605" t="inlineStr">
         <is>
           <t>HURC</t>
         </is>
       </c>
-      <c r="E1605" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1605" t="inlineStr"/>
       <c r="G1605" t="inlineStr"/>
       <c r="H1605" t="n">
         <v>1</v>
@@ -63973,17 +63961,17 @@
       <c r="C1606" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="D1606" t="inlineStr">
+      <c r="D1606" t="inlineStr"/>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>KEY TRONIC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1606" t="inlineStr">
         <is>
           <t>KTCC</t>
         </is>
       </c>
-      <c r="E1606" t="inlineStr">
-        <is>
-          <t>KEY TRONIC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1606" t="inlineStr"/>
       <c r="G1606" t="inlineStr"/>
       <c r="H1606" t="n">
         <v>2</v>
@@ -64008,17 +63996,17 @@
       <c r="C1607" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="D1607" t="inlineStr">
+      <c r="D1607" t="inlineStr"/>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1607" t="inlineStr">
         <is>
           <t>SGMA</t>
         </is>
       </c>
-      <c r="E1607" t="inlineStr">
-        <is>
-          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1607" t="inlineStr"/>
       <c r="G1607" t="inlineStr"/>
       <c r="H1607" t="n">
         <v>6</v>
@@ -64043,17 +64031,17 @@
       <c r="C1608" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="D1608" t="inlineStr">
+      <c r="D1608" t="inlineStr"/>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1608" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1608" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1608" t="inlineStr"/>
       <c r="G1608" t="inlineStr"/>
       <c r="H1608" t="n">
         <v>1</v>
@@ -64078,17 +64066,17 @@
       <c r="C1609" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="D1609" t="inlineStr">
+      <c r="D1609" t="inlineStr"/>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>LAKELAND IND INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1609" t="inlineStr">
         <is>
           <t>LAKE</t>
         </is>
       </c>
-      <c r="E1609" t="inlineStr">
-        <is>
-          <t>LAKELAND IND INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1609" t="inlineStr"/>
       <c r="G1609" t="inlineStr"/>
       <c r="H1609" t="n">
         <v>1</v>
@@ -64113,17 +64101,17 @@
       <c r="C1610" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="D1610" t="inlineStr">
+      <c r="D1610" t="inlineStr"/>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC COM UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1610" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1610" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC COM UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1610" t="inlineStr"/>
       <c r="G1610" t="inlineStr"/>
       <c r="H1610" t="n">
         <v>1</v>
@@ -64148,17 +64136,17 @@
       <c r="C1611" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="D1611" t="inlineStr">
+      <c r="D1611" t="inlineStr"/>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>TITAN MACHINERY INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1611" t="inlineStr">
         <is>
           <t>TITN</t>
         </is>
       </c>
-      <c r="E1611" t="inlineStr">
-        <is>
-          <t>TITAN MACHINERY INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1611" t="inlineStr"/>
       <c r="G1611" t="inlineStr"/>
       <c r="H1611" t="n">
         <v>1</v>
@@ -64183,19 +64171,15 @@
       <c r="C1612" s="2" t="n">
         <v>45222</v>
       </c>
-      <c r="D1612" t="inlineStr">
+      <c r="D1612" t="inlineStr"/>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1612" t="inlineStr">
         <is>
           <t>SGMA</t>
-        </is>
-      </c>
-      <c r="E1612" t="inlineStr">
-        <is>
-          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1612" t="inlineStr">
-        <is>
-          <t>EQ</t>
         </is>
       </c>
       <c r="G1612" t="inlineStr"/>
@@ -64222,17 +64206,17 @@
       <c r="C1613" s="2" t="n">
         <v>45222</v>
       </c>
-      <c r="D1613" t="inlineStr">
+      <c r="D1613" t="inlineStr"/>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>KEY TRONIC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1613" t="inlineStr">
         <is>
           <t>KTCC</t>
         </is>
       </c>
-      <c r="E1613" t="inlineStr">
-        <is>
-          <t>KEY TRONIC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1613" t="inlineStr"/>
       <c r="G1613" t="inlineStr"/>
       <c r="H1613" t="n">
         <v>1</v>
@@ -64257,19 +64241,15 @@
       <c r="C1614" s="2" t="n">
         <v>45222</v>
       </c>
-      <c r="D1614" t="inlineStr">
+      <c r="D1614" t="inlineStr"/>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC COM UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1614" t="inlineStr">
         <is>
           <t>MG</t>
-        </is>
-      </c>
-      <c r="E1614" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC COM UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1614" t="inlineStr">
-        <is>
-          <t>EQ</t>
         </is>
       </c>
       <c r="G1614" t="inlineStr"/>
@@ -64296,17 +64276,17 @@
       <c r="C1615" s="2" t="n">
         <v>45222</v>
       </c>
-      <c r="D1615" t="inlineStr">
+      <c r="D1615" t="inlineStr"/>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>FONAR CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1615" t="inlineStr">
         <is>
           <t>FONR</t>
         </is>
       </c>
-      <c r="E1615" t="inlineStr">
-        <is>
-          <t>FONAR CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1615" t="inlineStr"/>
       <c r="G1615" t="inlineStr"/>
       <c r="H1615" t="n">
         <v>-1</v>
@@ -64331,17 +64311,17 @@
       <c r="C1616" s="2" t="n">
         <v>45222</v>
       </c>
-      <c r="D1616" t="inlineStr">
+      <c r="D1616" t="inlineStr"/>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1616" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1616" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1616" t="inlineStr"/>
       <c r="G1616" t="inlineStr"/>
       <c r="H1616" t="n">
         <v>1</v>
@@ -64366,17 +64346,17 @@
       <c r="C1617" s="2" t="n">
         <v>45222</v>
       </c>
-      <c r="D1617" t="inlineStr">
+      <c r="D1617" t="inlineStr"/>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1617" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1617" t="inlineStr">
-        <is>
-          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1617" t="inlineStr"/>
       <c r="G1617" t="inlineStr"/>
       <c r="H1617" t="n">
         <v>3</v>
@@ -64401,17 +64381,17 @@
       <c r="C1618" s="2" t="n">
         <v>45222</v>
       </c>
-      <c r="D1618" t="inlineStr">
+      <c r="D1618" t="inlineStr"/>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>VSE CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1618" t="inlineStr">
         <is>
           <t>VSEC</t>
         </is>
       </c>
-      <c r="E1618" t="inlineStr">
-        <is>
-          <t>VSE CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1618" t="inlineStr"/>
       <c r="G1618" t="inlineStr"/>
       <c r="H1618" t="n">
         <v>1</v>
@@ -64436,17 +64416,17 @@
       <c r="C1619" s="2" t="n">
         <v>45222</v>
       </c>
-      <c r="D1619" t="inlineStr">
+      <c r="D1619" t="inlineStr"/>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECH INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1619" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1619" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECH INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1619" t="inlineStr"/>
       <c r="G1619" t="inlineStr"/>
       <c r="H1619" t="n">
         <v>1</v>
@@ -64471,17 +64451,17 @@
       <c r="C1620" s="2" t="n">
         <v>45222</v>
       </c>
-      <c r="D1620" t="inlineStr">
+      <c r="D1620" t="inlineStr"/>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>BEAZER HOMES USA INC COM NEW UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1620" t="inlineStr">
         <is>
           <t>BZH</t>
         </is>
       </c>
-      <c r="E1620" t="inlineStr">
-        <is>
-          <t>BEAZER HOMES USA INC COM NEW UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1620" t="inlineStr"/>
       <c r="G1620" t="inlineStr"/>
       <c r="H1620" t="n">
         <v>1</v>
@@ -64506,17 +64486,17 @@
       <c r="C1621" s="2" t="n">
         <v>45215</v>
       </c>
-      <c r="D1621" t="inlineStr">
+      <c r="D1621" t="inlineStr"/>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES REC 10/16/23 PAY 10/16/23 RATE 0.00000000 QTY 0.00000000</t>
+        </is>
+      </c>
+      <c r="F1621" t="inlineStr">
         <is>
           <t>HURC</t>
         </is>
       </c>
-      <c r="E1621" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES REC 10/16/23 PAY 10/16/23 RATE 0.00000000 QTY 0.00000000</t>
-        </is>
-      </c>
-      <c r="F1621" t="inlineStr"/>
       <c r="G1621" t="inlineStr"/>
       <c r="H1621" t="n">
         <v>0</v>
@@ -64541,19 +64521,15 @@
       <c r="C1622" s="2" t="n">
         <v>45215</v>
       </c>
-      <c r="D1622" t="inlineStr">
+      <c r="D1622" t="inlineStr"/>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>BASSETT FURNITURE UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1622" t="inlineStr">
         <is>
           <t>BSET</t>
-        </is>
-      </c>
-      <c r="E1622" t="inlineStr">
-        <is>
-          <t>BASSETT FURNITURE UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1622" t="inlineStr">
-        <is>
-          <t>EQ</t>
         </is>
       </c>
       <c r="G1622" t="inlineStr"/>
@@ -64580,17 +64556,17 @@
       <c r="C1623" s="2" t="n">
         <v>45215</v>
       </c>
-      <c r="D1623" t="inlineStr">
+      <c r="D1623" t="inlineStr"/>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>ROCKY BRANDS INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1623" t="inlineStr">
         <is>
           <t>RCKY</t>
         </is>
       </c>
-      <c r="E1623" t="inlineStr">
-        <is>
-          <t>ROCKY BRANDS INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1623" t="inlineStr"/>
       <c r="G1623" t="inlineStr"/>
       <c r="H1623" t="n">
         <v>1</v>
@@ -64615,17 +64591,17 @@
       <c r="C1624" s="2" t="n">
         <v>45215</v>
       </c>
-      <c r="D1624" t="inlineStr">
+      <c r="D1624" t="inlineStr"/>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1624" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1624" t="inlineStr">
-        <is>
-          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1624" t="inlineStr"/>
       <c r="G1624" t="inlineStr"/>
       <c r="H1624" t="n">
         <v>2</v>
@@ -64650,17 +64626,17 @@
       <c r="C1625" s="2" t="n">
         <v>45215</v>
       </c>
-      <c r="D1625" t="inlineStr">
+      <c r="D1625" t="inlineStr"/>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1625" t="inlineStr">
         <is>
           <t>PKOH</t>
         </is>
       </c>
-      <c r="E1625" t="inlineStr">
-        <is>
-          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1625" t="inlineStr"/>
       <c r="G1625" t="inlineStr"/>
       <c r="H1625" t="n">
         <v>1</v>
@@ -64685,17 +64661,17 @@
       <c r="C1626" s="2" t="n">
         <v>45215</v>
       </c>
-      <c r="D1626" t="inlineStr">
+      <c r="D1626" t="inlineStr"/>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1626" t="inlineStr">
         <is>
           <t>SGMA</t>
         </is>
       </c>
-      <c r="E1626" t="inlineStr">
-        <is>
-          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1626" t="inlineStr"/>
       <c r="G1626" t="inlineStr"/>
       <c r="H1626" t="n">
         <v>9</v>
@@ -64720,17 +64696,17 @@
       <c r="C1627" s="2" t="n">
         <v>45215</v>
       </c>
-      <c r="D1627" t="inlineStr">
+      <c r="D1627" t="inlineStr"/>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>FONAR CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1627" t="inlineStr">
         <is>
           <t>FONR</t>
         </is>
       </c>
-      <c r="E1627" t="inlineStr">
-        <is>
-          <t>FONAR CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1627" t="inlineStr"/>
       <c r="G1627" t="inlineStr"/>
       <c r="H1627" t="n">
         <v>1</v>
@@ -64755,17 +64731,17 @@
       <c r="C1628" s="2" t="n">
         <v>45215</v>
       </c>
-      <c r="D1628" t="inlineStr">
+      <c r="D1628" t="inlineStr"/>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>ENNIS INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1628" t="inlineStr">
         <is>
           <t>EBF</t>
         </is>
       </c>
-      <c r="E1628" t="inlineStr">
-        <is>
-          <t>ENNIS INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1628" t="inlineStr"/>
       <c r="G1628" t="inlineStr"/>
       <c r="H1628" t="n">
         <v>1</v>
@@ -64790,19 +64766,15 @@
       <c r="C1629" s="2" t="n">
         <v>45208</v>
       </c>
-      <c r="D1629" t="inlineStr">
+      <c r="D1629" t="inlineStr"/>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1629" t="inlineStr">
         <is>
           <t>SGMA</t>
-        </is>
-      </c>
-      <c r="E1629" t="inlineStr">
-        <is>
-          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1629" t="inlineStr">
-        <is>
-          <t>EQ</t>
         </is>
       </c>
       <c r="G1629" t="inlineStr"/>
@@ -64829,17 +64801,17 @@
       <c r="C1630" s="2" t="n">
         <v>45208</v>
       </c>
-      <c r="D1630" t="inlineStr">
+      <c r="D1630" t="inlineStr"/>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>FONAR CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1630" t="inlineStr">
         <is>
           <t>FONR</t>
         </is>
       </c>
-      <c r="E1630" t="inlineStr">
-        <is>
-          <t>FONAR CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1630" t="inlineStr"/>
       <c r="G1630" t="inlineStr"/>
       <c r="H1630" t="n">
         <v>1</v>
@@ -64864,17 +64836,17 @@
       <c r="C1631" s="2" t="n">
         <v>45208</v>
       </c>
-      <c r="D1631" t="inlineStr">
+      <c r="D1631" t="inlineStr"/>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>KEY TRONIC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1631" t="inlineStr">
         <is>
           <t>KTCC</t>
         </is>
       </c>
-      <c r="E1631" t="inlineStr">
-        <is>
-          <t>KEY TRONIC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1631" t="inlineStr"/>
       <c r="G1631" t="inlineStr"/>
       <c r="H1631" t="n">
         <v>1</v>
@@ -64899,17 +64871,17 @@
       <c r="C1632" s="2" t="n">
         <v>45208</v>
       </c>
-      <c r="D1632" t="inlineStr">
+      <c r="D1632" t="inlineStr"/>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1632" t="inlineStr">
         <is>
           <t>PKOH</t>
         </is>
       </c>
-      <c r="E1632" t="inlineStr">
-        <is>
-          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1632" t="inlineStr"/>
       <c r="G1632" t="inlineStr"/>
       <c r="H1632" t="n">
         <v>1</v>
@@ -64934,17 +64906,17 @@
       <c r="C1633" s="2" t="n">
         <v>45208</v>
       </c>
-      <c r="D1633" t="inlineStr">
+      <c r="D1633" t="inlineStr"/>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>ROCKY BRANDS INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1633" t="inlineStr">
         <is>
           <t>RCKY</t>
         </is>
       </c>
-      <c r="E1633" t="inlineStr">
-        <is>
-          <t>ROCKY BRANDS INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1633" t="inlineStr"/>
       <c r="G1633" t="inlineStr"/>
       <c r="H1633" t="n">
         <v>1</v>
@@ -64969,17 +64941,17 @@
       <c r="C1634" s="2" t="n">
         <v>45208</v>
       </c>
-      <c r="D1634" t="inlineStr">
+      <c r="D1634" t="inlineStr"/>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>BEAZER HOMES USA INC COM NEW UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1634" t="inlineStr">
         <is>
           <t>BZH</t>
         </is>
       </c>
-      <c r="E1634" t="inlineStr">
-        <is>
-          <t>BEAZER HOMES USA INC COM NEW UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1634" t="inlineStr"/>
       <c r="G1634" t="inlineStr"/>
       <c r="H1634" t="n">
         <v>1</v>
@@ -65004,17 +64976,17 @@
       <c r="C1635" s="2" t="n">
         <v>45208</v>
       </c>
-      <c r="D1635" t="inlineStr">
+      <c r="D1635" t="inlineStr"/>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1635" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1635" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1635" t="inlineStr"/>
       <c r="G1635" t="inlineStr"/>
       <c r="H1635" t="n">
         <v>1</v>
@@ -65039,19 +65011,15 @@
       <c r="C1636" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="D1636" t="inlineStr">
+      <c r="D1636" t="inlineStr"/>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>FONAR CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1636" t="inlineStr">
         <is>
           <t>FONR</t>
-        </is>
-      </c>
-      <c r="E1636" t="inlineStr">
-        <is>
-          <t>FONAR CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1636" t="inlineStr">
-        <is>
-          <t>EQ</t>
         </is>
       </c>
       <c r="G1636" t="inlineStr"/>
@@ -65078,17 +65046,17 @@
       <c r="C1637" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="D1637" t="inlineStr">
+      <c r="D1637" t="inlineStr"/>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1637" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1637" t="inlineStr">
-        <is>
-          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1637" t="inlineStr"/>
       <c r="G1637" t="inlineStr"/>
       <c r="H1637" t="n">
         <v>3</v>
@@ -65113,17 +65081,17 @@
       <c r="C1638" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="D1638" t="inlineStr">
+      <c r="D1638" t="inlineStr"/>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1638" t="inlineStr">
         <is>
           <t>PKOH</t>
         </is>
       </c>
-      <c r="E1638" t="inlineStr">
-        <is>
-          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1638" t="inlineStr"/>
       <c r="G1638" t="inlineStr"/>
       <c r="H1638" t="n">
         <v>1</v>
@@ -65148,17 +65116,17 @@
       <c r="C1639" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="D1639" t="inlineStr">
+      <c r="D1639" t="inlineStr"/>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>ESCALADE INC DELAWARE UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1639" t="inlineStr">
         <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="E1639" t="inlineStr">
-        <is>
-          <t>ESCALADE INC DELAWARE UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1639" t="inlineStr"/>
       <c r="G1639" t="inlineStr"/>
       <c r="H1639" t="n">
         <v>1</v>
@@ -65183,17 +65151,17 @@
       <c r="C1640" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="D1640" t="inlineStr">
+      <c r="D1640" t="inlineStr"/>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>KIMBALL ELECTRONICS INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1640" t="inlineStr">
         <is>
           <t>KE</t>
         </is>
       </c>
-      <c r="E1640" t="inlineStr">
-        <is>
-          <t>KIMBALL ELECTRONICS INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1640" t="inlineStr"/>
       <c r="G1640" t="inlineStr"/>
       <c r="H1640" t="n">
         <v>1</v>
@@ -65218,17 +65186,17 @@
       <c r="C1641" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="D1641" t="inlineStr">
+      <c r="D1641" t="inlineStr"/>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>KEY TRONIC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1641" t="inlineStr">
         <is>
           <t>KTCC</t>
         </is>
       </c>
-      <c r="E1641" t="inlineStr">
-        <is>
-          <t>KEY TRONIC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1641" t="inlineStr"/>
       <c r="G1641" t="inlineStr"/>
       <c r="H1641" t="n">
         <v>2</v>
@@ -65253,17 +65221,17 @@
       <c r="C1642" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="D1642" t="inlineStr">
+      <c r="D1642" t="inlineStr"/>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>DUCOMMUN INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1642" t="inlineStr">
         <is>
           <t>DCO</t>
         </is>
       </c>
-      <c r="E1642" t="inlineStr">
-        <is>
-          <t>DUCOMMUN INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1642" t="inlineStr"/>
       <c r="G1642" t="inlineStr"/>
       <c r="H1642" t="n">
         <v>1</v>
@@ -65288,17 +65256,17 @@
       <c r="C1643" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="D1643" t="inlineStr">
+      <c r="D1643" t="inlineStr"/>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1643" t="inlineStr">
         <is>
           <t>SGMA</t>
         </is>
       </c>
-      <c r="E1643" t="inlineStr">
-        <is>
-          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1643" t="inlineStr"/>
       <c r="G1643" t="inlineStr"/>
       <c r="H1643" t="n">
         <v>12</v>
@@ -65323,17 +65291,17 @@
       <c r="C1644" s="2" t="n">
         <v>45201</v>
       </c>
-      <c r="D1644" t="inlineStr">
+      <c r="D1644" t="inlineStr"/>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>BEAZER HOMES USA INC COM NEW UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1644" t="inlineStr">
         <is>
           <t>BZH</t>
         </is>
       </c>
-      <c r="E1644" t="inlineStr">
-        <is>
-          <t>BEAZER HOMES USA INC COM NEW UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1644" t="inlineStr"/>
       <c r="G1644" t="inlineStr"/>
       <c r="H1644" t="n">
         <v>1</v>
@@ -65358,17 +65326,17 @@
       <c r="C1645" s="2" t="n">
         <v>45198</v>
       </c>
-      <c r="D1645" t="inlineStr">
+      <c r="D1645" t="inlineStr"/>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>COVENANT TRANSN GROUP INC CL A REC 09/30/23 PAY 09/30/23 RATE 0.00000000 QTY 0.00000000</t>
+        </is>
+      </c>
+      <c r="F1645" t="inlineStr">
         <is>
           <t>CVLG</t>
         </is>
       </c>
-      <c r="E1645" t="inlineStr">
-        <is>
-          <t>COVENANT TRANSN GROUP INC CL A REC 09/30/23 PAY 09/30/23 RATE 0.00000000 QTY 0.00000000</t>
-        </is>
-      </c>
-      <c r="F1645" t="inlineStr"/>
       <c r="G1645" t="inlineStr"/>
       <c r="H1645" t="n">
         <v>0</v>
@@ -65393,11 +65361,7 @@
       <c r="C1646" s="2" t="n">
         <v>45198</v>
       </c>
-      <c r="D1646" t="inlineStr">
-        <is>
-          <t>Dividend</t>
-        </is>
-      </c>
+      <c r="D1646" t="inlineStr"/>
       <c r="E1646" t="inlineStr">
         <is>
           <t>COVENANT TRANSN GROUP INC CL A REC 09/30/23 PAY 09/30/23 RATE 0.00000000 QTY 0.00000000</t>
@@ -65432,17 +65396,17 @@
       <c r="C1647" s="2" t="n">
         <v>45194</v>
       </c>
-      <c r="D1647" t="inlineStr">
+      <c r="D1647" t="inlineStr"/>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>NATURAL GAS SERVICES UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1647" t="inlineStr">
         <is>
           <t>NGS</t>
         </is>
       </c>
-      <c r="E1647" t="inlineStr">
-        <is>
-          <t>NATURAL GAS SERVICES UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1647" t="inlineStr"/>
       <c r="G1647" t="inlineStr"/>
       <c r="H1647" t="n">
         <v>2</v>
@@ -65467,17 +65431,17 @@
       <c r="C1648" s="2" t="n">
         <v>45194</v>
       </c>
-      <c r="D1648" t="inlineStr">
+      <c r="D1648" t="inlineStr"/>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>NACCO INDUSTRIES A UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1648" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E1648" t="inlineStr">
-        <is>
-          <t>NACCO INDUSTRIES A UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1648" t="inlineStr"/>
       <c r="G1648" t="inlineStr"/>
       <c r="H1648" t="n">
         <v>1</v>
@@ -65502,17 +65466,17 @@
       <c r="C1649" s="2" t="n">
         <v>45194</v>
       </c>
-      <c r="D1649" t="inlineStr">
+      <c r="D1649" t="inlineStr"/>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1649" t="inlineStr">
         <is>
           <t>SGMA</t>
         </is>
       </c>
-      <c r="E1649" t="inlineStr">
-        <is>
-          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1649" t="inlineStr"/>
       <c r="G1649" t="inlineStr"/>
       <c r="H1649" t="n">
         <v>1</v>
@@ -65537,17 +65501,17 @@
       <c r="C1650" s="2" t="n">
         <v>45194</v>
       </c>
-      <c r="D1650" t="inlineStr">
+      <c r="D1650" t="inlineStr"/>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>LAKELAND IND INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1650" t="inlineStr">
         <is>
           <t>LAKE</t>
         </is>
       </c>
-      <c r="E1650" t="inlineStr">
-        <is>
-          <t>LAKELAND IND INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1650" t="inlineStr"/>
       <c r="G1650" t="inlineStr"/>
       <c r="H1650" t="n">
         <v>1</v>
@@ -65572,17 +65536,17 @@
       <c r="C1651" s="2" t="n">
         <v>45194</v>
       </c>
-      <c r="D1651" t="inlineStr">
+      <c r="D1651" t="inlineStr"/>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>VSE CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1651" t="inlineStr">
         <is>
           <t>VSEC</t>
         </is>
       </c>
-      <c r="E1651" t="inlineStr">
-        <is>
-          <t>VSE CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1651" t="inlineStr"/>
       <c r="G1651" t="inlineStr"/>
       <c r="H1651" t="n">
         <v>1</v>
@@ -65607,17 +65571,17 @@
       <c r="C1652" s="2" t="n">
         <v>45194</v>
       </c>
-      <c r="D1652" t="inlineStr">
+      <c r="D1652" t="inlineStr"/>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>BEAZER HOMES USA INC COM NEW UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1652" t="inlineStr">
         <is>
           <t>BZH</t>
         </is>
       </c>
-      <c r="E1652" t="inlineStr">
-        <is>
-          <t>BEAZER HOMES USA INC COM NEW UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1652" t="inlineStr"/>
       <c r="G1652" t="inlineStr"/>
       <c r="H1652" t="n">
         <v>1</v>
@@ -65642,17 +65606,17 @@
       <c r="C1653" s="2" t="n">
         <v>45194</v>
       </c>
-      <c r="D1653" t="inlineStr">
+      <c r="D1653" t="inlineStr"/>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>DUCOMMUN INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1653" t="inlineStr">
         <is>
           <t>DCO</t>
         </is>
       </c>
-      <c r="E1653" t="inlineStr">
-        <is>
-          <t>DUCOMMUN INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1653" t="inlineStr"/>
       <c r="G1653" t="inlineStr"/>
       <c r="H1653" t="n">
         <v>1</v>
@@ -65677,17 +65641,17 @@
       <c r="C1654" s="2" t="n">
         <v>45194</v>
       </c>
-      <c r="D1654" t="inlineStr">
+      <c r="D1654" t="inlineStr"/>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1654" t="inlineStr">
         <is>
           <t>PKOH</t>
         </is>
       </c>
-      <c r="E1654" t="inlineStr">
-        <is>
-          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1654" t="inlineStr"/>
       <c r="G1654" t="inlineStr"/>
       <c r="H1654" t="n">
         <v>2</v>
@@ -65712,17 +65676,17 @@
       <c r="C1655" s="2" t="n">
         <v>45194</v>
       </c>
-      <c r="D1655" t="inlineStr">
+      <c r="D1655" t="inlineStr"/>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECH INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1655" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1655" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECH INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1655" t="inlineStr"/>
       <c r="G1655" t="inlineStr"/>
       <c r="H1655" t="n">
         <v>1</v>
@@ -65747,19 +65711,15 @@
       <c r="C1656" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="D1656" t="inlineStr">
+      <c r="D1656" t="inlineStr"/>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1656" t="inlineStr">
         <is>
           <t>HURC</t>
-        </is>
-      </c>
-      <c r="E1656" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1656" t="inlineStr">
-        <is>
-          <t>EQ</t>
         </is>
       </c>
       <c r="G1656" t="inlineStr"/>
@@ -65786,17 +65746,17 @@
       <c r="C1657" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="D1657" t="inlineStr">
+      <c r="D1657" t="inlineStr"/>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>BEAZER HOMES USA INC COM NEW UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1657" t="inlineStr">
         <is>
           <t>BZH</t>
         </is>
       </c>
-      <c r="E1657" t="inlineStr">
-        <is>
-          <t>BEAZER HOMES USA INC COM NEW UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1657" t="inlineStr"/>
       <c r="G1657" t="inlineStr"/>
       <c r="H1657" t="n">
         <v>1</v>
@@ -65821,17 +65781,17 @@
       <c r="C1658" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="D1658" t="inlineStr">
+      <c r="D1658" t="inlineStr"/>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>FONAR CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1658" t="inlineStr">
         <is>
           <t>FONR</t>
         </is>
       </c>
-      <c r="E1658" t="inlineStr">
-        <is>
-          <t>FONAR CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1658" t="inlineStr"/>
       <c r="G1658" t="inlineStr"/>
       <c r="H1658" t="n">
         <v>-1</v>
@@ -65856,17 +65816,17 @@
       <c r="C1659" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="D1659" t="inlineStr">
+      <c r="D1659" t="inlineStr"/>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>PANGAEA LOGISTICS SOLUTION LTD UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1659" t="inlineStr">
         <is>
           <t>PANL</t>
         </is>
       </c>
-      <c r="E1659" t="inlineStr">
-        <is>
-          <t>PANGAEA LOGISTICS SOLUTION LTD UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1659" t="inlineStr"/>
       <c r="G1659" t="inlineStr"/>
       <c r="H1659" t="n">
         <v>-2</v>
@@ -65891,17 +65851,17 @@
       <c r="C1660" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="D1660" t="inlineStr">
+      <c r="D1660" t="inlineStr"/>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1660" t="inlineStr">
         <is>
           <t>PKOH</t>
         </is>
       </c>
-      <c r="E1660" t="inlineStr">
-        <is>
-          <t>PARK OHIO HOLDINGS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1660" t="inlineStr"/>
       <c r="G1660" t="inlineStr"/>
       <c r="H1660" t="n">
         <v>2</v>
@@ -65926,17 +65886,17 @@
       <c r="C1661" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="D1661" t="inlineStr">
+      <c r="D1661" t="inlineStr"/>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>NATURAL GAS SERVICES UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1661" t="inlineStr">
         <is>
           <t>NGS</t>
         </is>
       </c>
-      <c r="E1661" t="inlineStr">
-        <is>
-          <t>NATURAL GAS SERVICES UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1661" t="inlineStr"/>
       <c r="G1661" t="inlineStr"/>
       <c r="H1661" t="n">
         <v>2</v>
@@ -65961,17 +65921,17 @@
       <c r="C1662" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="D1662" t="inlineStr">
+      <c r="D1662" t="inlineStr"/>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>ROCKY BRANDS INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1662" t="inlineStr">
         <is>
           <t>RCKY</t>
         </is>
       </c>
-      <c r="E1662" t="inlineStr">
-        <is>
-          <t>ROCKY BRANDS INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1662" t="inlineStr"/>
       <c r="G1662" t="inlineStr"/>
       <c r="H1662" t="n">
         <v>1</v>
@@ -65996,17 +65956,17 @@
       <c r="C1663" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="D1663" t="inlineStr">
+      <c r="D1663" t="inlineStr"/>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1663" t="inlineStr">
         <is>
           <t>SGMA</t>
         </is>
       </c>
-      <c r="E1663" t="inlineStr">
-        <is>
-          <t>SIGMATRON INTL UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1663" t="inlineStr"/>
       <c r="G1663" t="inlineStr"/>
       <c r="H1663" t="n">
         <v>15</v>
@@ -66031,17 +65991,17 @@
       <c r="C1664" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="D1664" t="inlineStr">
+      <c r="D1664" t="inlineStr"/>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1664" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1664" t="inlineStr">
-        <is>
-          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1664" t="inlineStr"/>
       <c r="G1664" t="inlineStr"/>
       <c r="H1664" t="n">
         <v>1</v>
@@ -66066,17 +66026,17 @@
       <c r="C1665" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="D1665" t="inlineStr">
+      <c r="D1665" t="inlineStr"/>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1665" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1665" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1665" t="inlineStr"/>
       <c r="G1665" t="inlineStr"/>
       <c r="H1665" t="n">
         <v>1</v>
@@ -66101,17 +66061,17 @@
       <c r="C1666" s="2" t="n">
         <v>45184</v>
       </c>
-      <c r="D1666" t="inlineStr">
+      <c r="D1666" t="inlineStr"/>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP REC 09/15/23 PAY 09/15/23 RATE 0.00000000 QTY 0.00000000</t>
+        </is>
+      </c>
+      <c r="F1666" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1666" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP REC 09/15/23 PAY 09/15/23 RATE 0.00000000 QTY 0.00000000</t>
-        </is>
-      </c>
-      <c r="F1666" t="inlineStr"/>
       <c r="G1666" t="inlineStr"/>
       <c r="H1666" t="n">
         <v>0</v>
@@ -66136,17 +66096,17 @@
       <c r="C1667" s="2" t="n">
         <v>45184</v>
       </c>
-      <c r="D1667" t="inlineStr">
+      <c r="D1667" t="inlineStr"/>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>ROCKY BRANDS INC REC 09/15/23 PAY 09/15/23 RATE 0.00000000 QTY 0.00000000</t>
+        </is>
+      </c>
+      <c r="F1667" t="inlineStr">
         <is>
           <t>RCKY</t>
         </is>
       </c>
-      <c r="E1667" t="inlineStr">
-        <is>
-          <t>ROCKY BRANDS INC REC 09/15/23 PAY 09/15/23 RATE 0.00000000 QTY 0.00000000</t>
-        </is>
-      </c>
-      <c r="F1667" t="inlineStr"/>
       <c r="G1667" t="inlineStr"/>
       <c r="H1667" t="n">
         <v>0</v>
@@ -66171,17 +66131,17 @@
       <c r="C1668" s="2" t="n">
         <v>45184</v>
       </c>
-      <c r="D1668" t="inlineStr">
+      <c r="D1668" t="inlineStr"/>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>PANGAEA LOGISTICS SOLUTION LTD REC 09/15/23 PAY 09/15/23 RATE 0.00000000 QTY 0.00000000</t>
+        </is>
+      </c>
+      <c r="F1668" t="inlineStr">
         <is>
           <t>PANL</t>
         </is>
       </c>
-      <c r="E1668" t="inlineStr">
-        <is>
-          <t>PANGAEA LOGISTICS SOLUTION LTD REC 09/15/23 PAY 09/15/23 RATE 0.00000000 QTY 0.00000000</t>
-        </is>
-      </c>
-      <c r="F1668" t="inlineStr"/>
       <c r="G1668" t="inlineStr"/>
       <c r="H1668" t="n">
         <v>0</v>
@@ -66206,17 +66166,17 @@
       <c r="C1669" s="2" t="n">
         <v>45184</v>
       </c>
-      <c r="D1669" t="inlineStr">
+      <c r="D1669" t="inlineStr"/>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>NACCO INDUSTRIES A REC 09/15/23 PAY 09/15/23 RATE 0.00000000 QTY 0.00000000</t>
+        </is>
+      </c>
+      <c r="F1669" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E1669" t="inlineStr">
-        <is>
-          <t>NACCO INDUSTRIES A REC 09/15/23 PAY 09/15/23 RATE 0.00000000 QTY 0.00000000</t>
-        </is>
-      </c>
-      <c r="F1669" t="inlineStr"/>
       <c r="G1669" t="inlineStr"/>
       <c r="H1669" t="n">
         <v>0</v>
@@ -66280,19 +66240,15 @@
       <c r="C1671" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1671" t="inlineStr">
+      <c r="D1671" t="inlineStr"/>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1671" t="inlineStr">
         <is>
           <t>BGFV</t>
-        </is>
-      </c>
-      <c r="E1671" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1671" t="inlineStr">
-        <is>
-          <t>EQ</t>
         </is>
       </c>
       <c r="G1671" t="inlineStr"/>
@@ -66319,17 +66275,17 @@
       <c r="C1672" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1672" t="inlineStr">
+      <c r="D1672" t="inlineStr"/>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1672" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1672" t="inlineStr">
-        <is>
-          <t>AMPCO PITTSBURGH CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1672" t="inlineStr"/>
       <c r="G1672" t="inlineStr"/>
       <c r="H1672" t="n">
         <v>1</v>
@@ -66354,17 +66310,17 @@
       <c r="C1673" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1673" t="inlineStr">
+      <c r="D1673" t="inlineStr"/>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>TITAN MACHINERY INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1673" t="inlineStr">
         <is>
           <t>TITN</t>
         </is>
       </c>
-      <c r="E1673" t="inlineStr">
-        <is>
-          <t>TITAN MACHINERY INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1673" t="inlineStr"/>
       <c r="G1673" t="inlineStr"/>
       <c r="H1673" t="n">
         <v>1</v>
@@ -66389,17 +66345,17 @@
       <c r="C1674" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1674" t="inlineStr">
+      <c r="D1674" t="inlineStr"/>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>BASSETT FURNITURE UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1674" t="inlineStr">
         <is>
           <t>BSET</t>
         </is>
       </c>
-      <c r="E1674" t="inlineStr">
-        <is>
-          <t>BASSETT FURNITURE UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1674" t="inlineStr"/>
       <c r="G1674" t="inlineStr"/>
       <c r="H1674" t="n">
         <v>-1</v>
@@ -66424,17 +66380,17 @@
       <c r="C1675" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1675" t="inlineStr">
+      <c r="D1675" t="inlineStr"/>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>ROCKY BRANDS INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1675" t="inlineStr">
         <is>
           <t>RCKY</t>
         </is>
       </c>
-      <c r="E1675" t="inlineStr">
-        <is>
-          <t>ROCKY BRANDS INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1675" t="inlineStr"/>
       <c r="G1675" t="inlineStr"/>
       <c r="H1675" t="n">
         <v>1</v>
@@ -66459,17 +66415,17 @@
       <c r="C1676" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1676" t="inlineStr">
+      <c r="D1676" t="inlineStr"/>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>NACCO INDUSTRIES A UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1676" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E1676" t="inlineStr">
-        <is>
-          <t>NACCO INDUSTRIES A UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1676" t="inlineStr"/>
       <c r="G1676" t="inlineStr"/>
       <c r="H1676" t="n">
         <v>1</v>
@@ -66494,17 +66450,17 @@
       <c r="C1677" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1677" t="inlineStr">
+      <c r="D1677" t="inlineStr"/>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>PANGAEA LOGISTICS SOLUTION LTD UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1677" t="inlineStr">
         <is>
           <t>PANL</t>
         </is>
       </c>
-      <c r="E1677" t="inlineStr">
-        <is>
-          <t>PANGAEA LOGISTICS SOLUTION LTD UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1677" t="inlineStr"/>
       <c r="G1677" t="inlineStr"/>
       <c r="H1677" t="n">
         <v>-5</v>
@@ -66529,17 +66485,17 @@
       <c r="C1678" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1678" t="inlineStr">
+      <c r="D1678" t="inlineStr"/>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>ESCALADE INC DELAWARE UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1678" t="inlineStr">
         <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="E1678" t="inlineStr">
-        <is>
-          <t>ESCALADE INC DELAWARE UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1678" t="inlineStr"/>
       <c r="G1678" t="inlineStr"/>
       <c r="H1678" t="n">
         <v>1</v>
@@ -66564,17 +66520,17 @@
       <c r="C1679" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1679" t="inlineStr">
+      <c r="D1679" t="inlineStr"/>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>KEY TRONIC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1679" t="inlineStr">
         <is>
           <t>KTCC</t>
         </is>
       </c>
-      <c r="E1679" t="inlineStr">
-        <is>
-          <t>KEY TRONIC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1679" t="inlineStr"/>
       <c r="G1679" t="inlineStr"/>
       <c r="H1679" t="n">
         <v>2</v>
@@ -66599,17 +66555,17 @@
       <c r="C1680" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1680" t="inlineStr">
+      <c r="D1680" t="inlineStr"/>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>FONAR CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1680" t="inlineStr">
         <is>
           <t>FONR</t>
         </is>
       </c>
-      <c r="E1680" t="inlineStr">
-        <is>
-          <t>FONAR CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1680" t="inlineStr"/>
       <c r="G1680" t="inlineStr"/>
       <c r="H1680" t="n">
         <v>-3</v>
@@ -66634,17 +66590,17 @@
       <c r="C1681" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1681" t="inlineStr">
+      <c r="D1681" t="inlineStr"/>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECH INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1681" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1681" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECH INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1681" t="inlineStr"/>
       <c r="G1681" t="inlineStr"/>
       <c r="H1681" t="n">
         <v>1</v>
@@ -66669,17 +66625,17 @@
       <c r="C1682" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1682" t="inlineStr">
+      <c r="D1682" t="inlineStr"/>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC COM UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1682" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1682" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC COM UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1682" t="inlineStr"/>
       <c r="G1682" t="inlineStr"/>
       <c r="H1682" t="n">
         <v>2</v>
@@ -66704,17 +66660,17 @@
       <c r="C1683" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1683" t="inlineStr">
+      <c r="D1683" t="inlineStr"/>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>DUCOMMUN INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1683" t="inlineStr">
         <is>
           <t>DCO</t>
         </is>
       </c>
-      <c r="E1683" t="inlineStr">
-        <is>
-          <t>DUCOMMUN INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1683" t="inlineStr"/>
       <c r="G1683" t="inlineStr"/>
       <c r="H1683" t="n">
         <v>-1</v>
@@ -66739,17 +66695,17 @@
       <c r="C1684" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1684" t="inlineStr">
+      <c r="D1684" t="inlineStr"/>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>COVENANT TRANSN GROUP INC CL A UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1684" t="inlineStr">
         <is>
           <t>CVLG</t>
         </is>
       </c>
-      <c r="E1684" t="inlineStr">
-        <is>
-          <t>COVENANT TRANSN GROUP INC CL A UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1684" t="inlineStr"/>
       <c r="G1684" t="inlineStr"/>
       <c r="H1684" t="n">
         <v>1</v>
@@ -66774,17 +66730,17 @@
       <c r="C1685" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1685" t="inlineStr">
+      <c r="D1685" t="inlineStr"/>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1685" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1685" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1685" t="inlineStr"/>
       <c r="G1685" t="inlineStr"/>
       <c r="H1685" t="n">
         <v>1</v>
@@ -66809,17 +66765,17 @@
       <c r="C1686" s="2" t="n">
         <v>45180</v>
       </c>
-      <c r="D1686" t="inlineStr">
+      <c r="D1686" t="inlineStr"/>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>CLARUS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1686" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1686" t="inlineStr">
-        <is>
-          <t>CLARUS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1686" t="inlineStr"/>
       <c r="G1686" t="inlineStr"/>
       <c r="H1686" t="n">
         <v>1</v>
@@ -66844,19 +66800,15 @@
       <c r="C1687" s="2" t="n">
         <v>45174</v>
       </c>
-      <c r="D1687" t="inlineStr">
+      <c r="D1687" t="inlineStr"/>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>DUCOMMUN INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1687" t="inlineStr">
         <is>
           <t>DCO</t>
-        </is>
-      </c>
-      <c r="E1687" t="inlineStr">
-        <is>
-          <t>DUCOMMUN INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1687" t="inlineStr">
-        <is>
-          <t>EQ</t>
         </is>
       </c>
       <c r="G1687" t="inlineStr"/>
@@ -66883,17 +66835,17 @@
       <c r="C1688" s="2" t="n">
         <v>45174</v>
       </c>
-      <c r="D1688" t="inlineStr">
+      <c r="D1688" t="inlineStr"/>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1688" t="inlineStr">
         <is>
           <t>HURC</t>
         </is>
       </c>
-      <c r="E1688" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1688" t="inlineStr"/>
       <c r="G1688" t="inlineStr"/>
       <c r="H1688" t="n">
         <v>-1</v>
@@ -66918,17 +66870,17 @@
       <c r="C1689" s="2" t="n">
         <v>45174</v>
       </c>
-      <c r="D1689" t="inlineStr">
+      <c r="D1689" t="inlineStr"/>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1689" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1689" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1689" t="inlineStr"/>
       <c r="G1689" t="inlineStr"/>
       <c r="H1689" t="n">
         <v>1</v>
@@ -66953,17 +66905,17 @@
       <c r="C1690" s="2" t="n">
         <v>45174</v>
       </c>
-      <c r="D1690" t="inlineStr">
+      <c r="D1690" t="inlineStr"/>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1690" t="inlineStr">
         <is>
           <t>HURC</t>
         </is>
       </c>
-      <c r="E1690" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1690" t="inlineStr"/>
       <c r="G1690" t="inlineStr"/>
       <c r="H1690" t="n">
         <v>-1</v>
@@ -66988,17 +66940,17 @@
       <c r="C1691" s="2" t="n">
         <v>45174</v>
       </c>
-      <c r="D1691" t="inlineStr">
+      <c r="D1691" t="inlineStr"/>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1691" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1691" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1691" t="inlineStr"/>
       <c r="G1691" t="inlineStr"/>
       <c r="H1691" t="n">
         <v>1</v>
@@ -67023,17 +66975,17 @@
       <c r="C1692" s="2" t="n">
         <v>45174</v>
       </c>
-      <c r="D1692" t="inlineStr">
+      <c r="D1692" t="inlineStr"/>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>LAKELAND IND INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1692" t="inlineStr">
         <is>
           <t>LAKE</t>
         </is>
       </c>
-      <c r="E1692" t="inlineStr">
-        <is>
-          <t>LAKELAND IND INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1692" t="inlineStr"/>
       <c r="G1692" t="inlineStr"/>
       <c r="H1692" t="n">
         <v>-1</v>
@@ -67058,17 +67010,17 @@
       <c r="C1693" s="2" t="n">
         <v>45174</v>
       </c>
-      <c r="D1693" t="inlineStr">
+      <c r="D1693" t="inlineStr"/>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>FONAR CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1693" t="inlineStr">
         <is>
           <t>FONR</t>
         </is>
       </c>
-      <c r="E1693" t="inlineStr">
-        <is>
-          <t>FONAR CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1693" t="inlineStr"/>
       <c r="G1693" t="inlineStr"/>
       <c r="H1693" t="n">
         <v>-12</v>
@@ -67093,17 +67045,17 @@
       <c r="C1694" s="2" t="n">
         <v>45174</v>
       </c>
-      <c r="D1694" t="inlineStr">
+      <c r="D1694" t="inlineStr"/>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>PANGAEA LOGISTICS SOLUTION LTD UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1694" t="inlineStr">
         <is>
           <t>PANL</t>
         </is>
       </c>
-      <c r="E1694" t="inlineStr">
-        <is>
-          <t>PANGAEA LOGISTICS SOLUTION LTD UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1694" t="inlineStr"/>
       <c r="G1694" t="inlineStr"/>
       <c r="H1694" t="n">
         <v>-39</v>
@@ -67128,17 +67080,17 @@
       <c r="C1695" s="2" t="n">
         <v>45174</v>
       </c>
-      <c r="D1695" t="inlineStr">
+      <c r="D1695" t="inlineStr"/>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>CLARUS CORP UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1695" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1695" t="inlineStr">
-        <is>
-          <t>CLARUS CORP UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1695" t="inlineStr"/>
       <c r="G1695" t="inlineStr"/>
       <c r="H1695" t="n">
         <v>-1</v>
@@ -67163,17 +67115,17 @@
       <c r="C1696" s="2" t="n">
         <v>45174</v>
       </c>
-      <c r="D1696" t="inlineStr">
+      <c r="D1696" t="inlineStr"/>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>ROCKY BRANDS INC UNSOLICITED TRADE</t>
+        </is>
+      </c>
+      <c r="F1696" t="inlineStr">
         <is>
           <t>RCKY</t>
         </is>
       </c>
-      <c r="E1696" t="inlineStr">
-        <is>
-          <t>ROCKY BRANDS INC UNSOLICITED TRADE</t>
-        </is>
-      </c>
-      <c r="F1696" t="inlineStr"/>
       <c r="G1696" t="inlineStr"/>
       <c r="H1696" t="n">
         <v>1</v>
@@ -67198,17 +67150,17 @@
       <c r="C1697" s="2" t="n">
         <v>45174</v>
       </c>
-      <c r="D1697" t="inlineStr">
+      <c r="D1697" t="inlineStr"/>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>ESCALADE INC                  CASH DIV  ON       8 SHS      REC 08/29/23 PAY 09/05/23</t>
+        </is>
+      </c>
+      <c r="F1697" t="inlineStr">
         <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="E1697" t="inlineStr">
-        <is>
-          <t>ESCALADE INC                  CASH DIV  ON       8 SHS      REC 08/29/23 PAY 09/05/23</t>
-        </is>
-      </c>
-      <c r="F1697" t="inlineStr"/>
       <c r="G1697" t="inlineStr"/>
       <c r="H1697" t="n">
         <v>0</v>
@@ -67272,17 +67224,17 @@
       <c r="C1699" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1699" t="inlineStr">
+      <c r="D1699" t="inlineStr"/>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>VISHAY PRECISION GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1699" t="inlineStr">
         <is>
           <t>VPG</t>
         </is>
       </c>
-      <c r="E1699" t="inlineStr">
-        <is>
-          <t>VISHAY PRECISION GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1699" t="inlineStr"/>
       <c r="G1699" t="inlineStr"/>
       <c r="H1699" t="n">
         <v>1</v>
@@ -67307,17 +67259,17 @@
       <c r="C1700" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1700" t="inlineStr">
+      <c r="D1700" t="inlineStr"/>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP</t>
+        </is>
+      </c>
+      <c r="F1700" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1700" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP</t>
-        </is>
-      </c>
-      <c r="F1700" t="inlineStr"/>
       <c r="G1700" t="inlineStr"/>
       <c r="H1700" t="n">
         <v>1</v>
@@ -67342,17 +67294,17 @@
       <c r="C1701" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1701" t="inlineStr">
+      <c r="D1701" t="inlineStr"/>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>CLARUS CORPORATION            COMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1701" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1701" t="inlineStr">
-        <is>
-          <t>CLARUS CORPORATION            COMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1701" t="inlineStr"/>
       <c r="G1701" t="inlineStr"/>
       <c r="H1701" t="n">
         <v>-2</v>
@@ -67377,17 +67329,17 @@
       <c r="C1702" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1702" t="inlineStr">
+      <c r="D1702" t="inlineStr"/>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>KEY TRONIC CORP</t>
+        </is>
+      </c>
+      <c r="F1702" t="inlineStr">
         <is>
           <t>KTCC</t>
         </is>
       </c>
-      <c r="E1702" t="inlineStr">
-        <is>
-          <t>KEY TRONIC CORP</t>
-        </is>
-      </c>
-      <c r="F1702" t="inlineStr"/>
       <c r="G1702" t="inlineStr"/>
       <c r="H1702" t="n">
         <v>2</v>
@@ -67412,17 +67364,17 @@
       <c r="C1703" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1703" t="inlineStr">
+      <c r="D1703" t="inlineStr"/>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>FONAR CORPORATION</t>
+        </is>
+      </c>
+      <c r="F1703" t="inlineStr">
         <is>
           <t>FONR</t>
         </is>
       </c>
-      <c r="E1703" t="inlineStr">
-        <is>
-          <t>FONAR CORPORATION</t>
-        </is>
-      </c>
-      <c r="F1703" t="inlineStr"/>
       <c r="G1703" t="inlineStr"/>
       <c r="H1703" t="n">
         <v>-3</v>
@@ -67447,17 +67399,17 @@
       <c r="C1704" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1704" t="inlineStr">
+      <c r="D1704" t="inlineStr"/>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="F1704" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1704" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="F1704" t="inlineStr"/>
       <c r="G1704" t="inlineStr"/>
       <c r="H1704" t="n">
         <v>1</v>
@@ -67482,17 +67434,17 @@
       <c r="C1705" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1705" t="inlineStr">
+      <c r="D1705" t="inlineStr"/>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>DUCOMMUN INC</t>
+        </is>
+      </c>
+      <c r="F1705" t="inlineStr">
         <is>
           <t>DCO</t>
         </is>
       </c>
-      <c r="E1705" t="inlineStr">
-        <is>
-          <t>DUCOMMUN INC</t>
-        </is>
-      </c>
-      <c r="F1705" t="inlineStr"/>
       <c r="G1705" t="inlineStr"/>
       <c r="H1705" t="n">
         <v>-1</v>
@@ -67517,17 +67469,17 @@
       <c r="C1706" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1706" t="inlineStr">
+      <c r="D1706" t="inlineStr"/>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>***PANGAEA LOGISTICS SOLUTIONSLTD</t>
+        </is>
+      </c>
+      <c r="F1706" t="inlineStr">
         <is>
           <t>PANL</t>
         </is>
       </c>
-      <c r="E1706" t="inlineStr">
-        <is>
-          <t>***PANGAEA LOGISTICS SOLUTIONSLTD</t>
-        </is>
-      </c>
-      <c r="F1706" t="inlineStr"/>
       <c r="G1706" t="inlineStr"/>
       <c r="H1706" t="n">
         <v>-7</v>
@@ -67552,17 +67504,17 @@
       <c r="C1707" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1707" t="inlineStr">
+      <c r="D1707" t="inlineStr"/>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>LAKELAND INDS INC</t>
+        </is>
+      </c>
+      <c r="F1707" t="inlineStr">
         <is>
           <t>LAKE</t>
         </is>
       </c>
-      <c r="E1707" t="inlineStr">
-        <is>
-          <t>LAKELAND INDS INC</t>
-        </is>
-      </c>
-      <c r="F1707" t="inlineStr"/>
       <c r="G1707" t="inlineStr"/>
       <c r="H1707" t="n">
         <v>1</v>
@@ -67587,17 +67539,17 @@
       <c r="C1708" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1708" t="inlineStr">
+      <c r="D1708" t="inlineStr"/>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="F1708" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1708" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECHNOLOGIES INC</t>
-        </is>
-      </c>
-      <c r="F1708" t="inlineStr"/>
       <c r="G1708" t="inlineStr"/>
       <c r="H1708" t="n">
         <v>-1</v>
@@ -67622,17 +67574,17 @@
       <c r="C1709" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1709" t="inlineStr">
+      <c r="D1709" t="inlineStr"/>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>AMPCO-PITTSBURGH CORP</t>
+        </is>
+      </c>
+      <c r="F1709" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1709" t="inlineStr">
-        <is>
-          <t>AMPCO-PITTSBURGH CORP</t>
-        </is>
-      </c>
-      <c r="F1709" t="inlineStr"/>
       <c r="G1709" t="inlineStr"/>
       <c r="H1709" t="n">
         <v>1</v>
@@ -67657,17 +67609,17 @@
       <c r="C1710" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1710" t="inlineStr">
+      <c r="D1710" t="inlineStr"/>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>TITAN MACHINERY INC</t>
+        </is>
+      </c>
+      <c r="F1710" t="inlineStr">
         <is>
           <t>TITN</t>
         </is>
       </c>
-      <c r="E1710" t="inlineStr">
-        <is>
-          <t>TITAN MACHINERY INC</t>
-        </is>
-      </c>
-      <c r="F1710" t="inlineStr"/>
       <c r="G1710" t="inlineStr"/>
       <c r="H1710" t="n">
         <v>-1</v>
@@ -67692,17 +67644,17 @@
       <c r="C1711" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="D1711" t="inlineStr">
+      <c r="D1711" t="inlineStr"/>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1711" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1711" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1711" t="inlineStr"/>
       <c r="G1711" t="inlineStr"/>
       <c r="H1711" t="n">
         <v>1</v>
@@ -67727,17 +67679,17 @@
       <c r="C1712" s="2" t="n">
         <v>45163</v>
       </c>
-      <c r="D1712" t="inlineStr">
+      <c r="D1712" t="inlineStr"/>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>CLARUS CORPORATION            COMMON STOCK                  CASH DIV  ON      10 SHS      REC 08/14/23 PAY 08/25/23</t>
+        </is>
+      </c>
+      <c r="F1712" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1712" t="inlineStr">
-        <is>
-          <t>CLARUS CORPORATION            COMMON STOCK                  CASH DIV  ON      10 SHS      REC 08/14/23 PAY 08/25/23</t>
-        </is>
-      </c>
-      <c r="F1712" t="inlineStr"/>
       <c r="G1712" t="inlineStr"/>
       <c r="H1712" t="n">
         <v>0</v>
@@ -67762,17 +67714,17 @@
       <c r="C1713" s="2" t="n">
         <v>45163</v>
       </c>
-      <c r="D1713" t="inlineStr">
+      <c r="D1713" t="inlineStr"/>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>BASSETT FURNITURE INDS INC    CASH DIV  ON      13 SHS      REC 08/11/23 PAY 08/25/23</t>
+        </is>
+      </c>
+      <c r="F1713" t="inlineStr">
         <is>
           <t>BSET</t>
         </is>
       </c>
-      <c r="E1713" t="inlineStr">
-        <is>
-          <t>BASSETT FURNITURE INDS INC    CASH DIV  ON      13 SHS      REC 08/11/23 PAY 08/25/23</t>
-        </is>
-      </c>
-      <c r="F1713" t="inlineStr"/>
       <c r="G1713" t="inlineStr"/>
       <c r="H1713" t="n">
         <v>0</v>
@@ -67836,17 +67788,17 @@
       <c r="C1715" s="2" t="n">
         <v>45160</v>
       </c>
-      <c r="D1715" t="inlineStr">
+      <c r="D1715" t="inlineStr"/>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>LAKELAND INDS INC             CASH DIV  ON       6 SHS      REC 08/15/23 PAY 08/22/23</t>
+        </is>
+      </c>
+      <c r="F1715" t="inlineStr">
         <is>
           <t>LAKE</t>
         </is>
       </c>
-      <c r="E1715" t="inlineStr">
-        <is>
-          <t>LAKELAND INDS INC             CASH DIV  ON       6 SHS      REC 08/15/23 PAY 08/22/23</t>
-        </is>
-      </c>
-      <c r="F1715" t="inlineStr"/>
       <c r="G1715" t="inlineStr"/>
       <c r="H1715" t="n">
         <v>0</v>
@@ -67910,17 +67862,17 @@
       <c r="C1717" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1717" t="inlineStr">
+      <c r="D1717" t="inlineStr"/>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>ESCALADE INC</t>
+        </is>
+      </c>
+      <c r="F1717" t="inlineStr">
         <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="E1717" t="inlineStr">
-        <is>
-          <t>ESCALADE INC</t>
-        </is>
-      </c>
-      <c r="F1717" t="inlineStr"/>
       <c r="G1717" t="inlineStr"/>
       <c r="H1717" t="n">
         <v>1</v>
@@ -67945,17 +67897,17 @@
       <c r="C1718" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1718" t="inlineStr">
+      <c r="D1718" t="inlineStr"/>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP</t>
+        </is>
+      </c>
+      <c r="F1718" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1718" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP</t>
-        </is>
-      </c>
-      <c r="F1718" t="inlineStr"/>
       <c r="G1718" t="inlineStr"/>
       <c r="H1718" t="n">
         <v>2</v>
@@ -67980,17 +67932,17 @@
       <c r="C1719" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1719" t="inlineStr">
+      <c r="D1719" t="inlineStr"/>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>LAKELAND INDS INC</t>
+        </is>
+      </c>
+      <c r="F1719" t="inlineStr">
         <is>
           <t>LAKE</t>
         </is>
       </c>
-      <c r="E1719" t="inlineStr">
-        <is>
-          <t>LAKELAND INDS INC</t>
-        </is>
-      </c>
-      <c r="F1719" t="inlineStr"/>
       <c r="G1719" t="inlineStr"/>
       <c r="H1719" t="n">
         <v>1</v>
@@ -68015,17 +67967,17 @@
       <c r="C1720" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1720" t="inlineStr">
+      <c r="D1720" t="inlineStr"/>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>TITAN MACHINERY INC</t>
+        </is>
+      </c>
+      <c r="F1720" t="inlineStr">
         <is>
           <t>TITN</t>
         </is>
       </c>
-      <c r="E1720" t="inlineStr">
-        <is>
-          <t>TITAN MACHINERY INC</t>
-        </is>
-      </c>
-      <c r="F1720" t="inlineStr"/>
       <c r="G1720" t="inlineStr"/>
       <c r="H1720" t="n">
         <v>1</v>
@@ -68050,17 +68002,17 @@
       <c r="C1721" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1721" t="inlineStr">
+      <c r="D1721" t="inlineStr"/>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
+        </is>
+      </c>
+      <c r="F1721" t="inlineStr">
         <is>
           <t>EBF</t>
         </is>
       </c>
-      <c r="E1721" t="inlineStr">
-        <is>
-          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
-        </is>
-      </c>
-      <c r="F1721" t="inlineStr"/>
       <c r="G1721" t="inlineStr"/>
       <c r="H1721" t="n">
         <v>1</v>
@@ -68085,17 +68037,17 @@
       <c r="C1722" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1722" t="inlineStr">
+      <c r="D1722" t="inlineStr"/>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>BASSETT FURNITURE INDS INC</t>
+        </is>
+      </c>
+      <c r="F1722" t="inlineStr">
         <is>
           <t>BSET</t>
         </is>
       </c>
-      <c r="E1722" t="inlineStr">
-        <is>
-          <t>BASSETT FURNITURE INDS INC</t>
-        </is>
-      </c>
-      <c r="F1722" t="inlineStr"/>
       <c r="G1722" t="inlineStr"/>
       <c r="H1722" t="n">
         <v>1</v>
@@ -68120,17 +68072,17 @@
       <c r="C1723" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1723" t="inlineStr">
+      <c r="D1723" t="inlineStr"/>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>KEY TRONIC CORP</t>
+        </is>
+      </c>
+      <c r="F1723" t="inlineStr">
         <is>
           <t>KTCC</t>
         </is>
       </c>
-      <c r="E1723" t="inlineStr">
-        <is>
-          <t>KEY TRONIC CORP</t>
-        </is>
-      </c>
-      <c r="F1723" t="inlineStr"/>
       <c r="G1723" t="inlineStr"/>
       <c r="H1723" t="n">
         <v>3</v>
@@ -68155,17 +68107,17 @@
       <c r="C1724" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1724" t="inlineStr">
+      <c r="D1724" t="inlineStr"/>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>BEAZER HOMES USA INC</t>
+        </is>
+      </c>
+      <c r="F1724" t="inlineStr">
         <is>
           <t>BZH</t>
         </is>
       </c>
-      <c r="E1724" t="inlineStr">
-        <is>
-          <t>BEAZER HOMES USA INC</t>
-        </is>
-      </c>
-      <c r="F1724" t="inlineStr"/>
       <c r="G1724" t="inlineStr"/>
       <c r="H1724" t="n">
         <v>-6</v>
@@ -68190,17 +68142,17 @@
       <c r="C1725" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1725" t="inlineStr">
+      <c r="D1725" t="inlineStr"/>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>DUCOMMUN INC</t>
+        </is>
+      </c>
+      <c r="F1725" t="inlineStr">
         <is>
           <t>DCO</t>
         </is>
       </c>
-      <c r="E1725" t="inlineStr">
-        <is>
-          <t>DUCOMMUN INC</t>
-        </is>
-      </c>
-      <c r="F1725" t="inlineStr"/>
       <c r="G1725" t="inlineStr"/>
       <c r="H1725" t="n">
         <v>1</v>
@@ -68225,17 +68177,17 @@
       <c r="C1726" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1726" t="inlineStr">
+      <c r="D1726" t="inlineStr"/>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="F1726" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1726" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="F1726" t="inlineStr"/>
       <c r="G1726" t="inlineStr"/>
       <c r="H1726" t="n">
         <v>2</v>
@@ -68260,17 +68212,17 @@
       <c r="C1727" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1727" t="inlineStr">
+      <c r="D1727" t="inlineStr"/>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1727" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1727" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1727" t="inlineStr"/>
       <c r="G1727" t="inlineStr"/>
       <c r="H1727" t="n">
         <v>2</v>
@@ -68295,17 +68247,17 @@
       <c r="C1728" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1728" t="inlineStr">
+      <c r="D1728" t="inlineStr"/>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="F1728" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1728" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECHNOLOGIES INC</t>
-        </is>
-      </c>
-      <c r="F1728" t="inlineStr"/>
       <c r="G1728" t="inlineStr"/>
       <c r="H1728" t="n">
         <v>1</v>
@@ -68330,17 +68282,17 @@
       <c r="C1729" s="2" t="n">
         <v>45159</v>
       </c>
-      <c r="D1729" t="inlineStr">
+      <c r="D1729" t="inlineStr"/>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>AMPCO-PITTSBURGH CORP</t>
+        </is>
+      </c>
+      <c r="F1729" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1729" t="inlineStr">
-        <is>
-          <t>AMPCO-PITTSBURGH CORP</t>
-        </is>
-      </c>
-      <c r="F1729" t="inlineStr"/>
       <c r="G1729" t="inlineStr"/>
       <c r="H1729" t="n">
         <v>5</v>
@@ -68365,17 +68317,17 @@
       <c r="C1730" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1730" t="inlineStr">
+      <c r="D1730" t="inlineStr"/>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>KIMBALL ELECTRONICS INC       COM</t>
+        </is>
+      </c>
+      <c r="F1730" t="inlineStr">
         <is>
           <t>KE</t>
         </is>
       </c>
-      <c r="E1730" t="inlineStr">
-        <is>
-          <t>KIMBALL ELECTRONICS INC       COM</t>
-        </is>
-      </c>
-      <c r="F1730" t="inlineStr"/>
       <c r="G1730" t="inlineStr"/>
       <c r="H1730" t="n">
         <v>1</v>
@@ -68400,17 +68352,17 @@
       <c r="C1731" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1731" t="inlineStr">
+      <c r="D1731" t="inlineStr"/>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>CLARUS CORPORATION            COMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1731" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1731" t="inlineStr">
-        <is>
-          <t>CLARUS CORPORATION            COMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1731" t="inlineStr"/>
       <c r="G1731" t="inlineStr"/>
       <c r="H1731" t="n">
         <v>-3</v>
@@ -68435,17 +68387,17 @@
       <c r="C1732" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1732" t="inlineStr">
+      <c r="D1732" t="inlineStr"/>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP</t>
+        </is>
+      </c>
+      <c r="F1732" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1732" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP</t>
-        </is>
-      </c>
-      <c r="F1732" t="inlineStr"/>
       <c r="G1732" t="inlineStr"/>
       <c r="H1732" t="n">
         <v>1</v>
@@ -68470,17 +68422,17 @@
       <c r="C1733" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1733" t="inlineStr">
+      <c r="D1733" t="inlineStr"/>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>NACCO INDUSTRIES INC-CL A</t>
+        </is>
+      </c>
+      <c r="F1733" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E1733" t="inlineStr">
-        <is>
-          <t>NACCO INDUSTRIES INC-CL A</t>
-        </is>
-      </c>
-      <c r="F1733" t="inlineStr"/>
       <c r="G1733" t="inlineStr"/>
       <c r="H1733" t="n">
         <v>1</v>
@@ -68505,17 +68457,17 @@
       <c r="C1734" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1734" t="inlineStr">
+      <c r="D1734" t="inlineStr"/>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
+        </is>
+      </c>
+      <c r="F1734" t="inlineStr">
         <is>
           <t>EBF</t>
         </is>
       </c>
-      <c r="E1734" t="inlineStr">
-        <is>
-          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
-        </is>
-      </c>
-      <c r="F1734" t="inlineStr"/>
       <c r="G1734" t="inlineStr"/>
       <c r="H1734" t="n">
         <v>1</v>
@@ -68540,17 +68492,17 @@
       <c r="C1735" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1735" t="inlineStr">
+      <c r="D1735" t="inlineStr"/>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>KEY TRONIC CORP</t>
+        </is>
+      </c>
+      <c r="F1735" t="inlineStr">
         <is>
           <t>KTCC</t>
         </is>
       </c>
-      <c r="E1735" t="inlineStr">
-        <is>
-          <t>KEY TRONIC CORP</t>
-        </is>
-      </c>
-      <c r="F1735" t="inlineStr"/>
       <c r="G1735" t="inlineStr"/>
       <c r="H1735" t="n">
         <v>1</v>
@@ -68575,17 +68527,17 @@
       <c r="C1736" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1736" t="inlineStr">
+      <c r="D1736" t="inlineStr"/>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>BEAZER HOMES USA INC</t>
+        </is>
+      </c>
+      <c r="F1736" t="inlineStr">
         <is>
           <t>BZH</t>
         </is>
       </c>
-      <c r="E1736" t="inlineStr">
-        <is>
-          <t>BEAZER HOMES USA INC</t>
-        </is>
-      </c>
-      <c r="F1736" t="inlineStr"/>
       <c r="G1736" t="inlineStr"/>
       <c r="H1736" t="n">
         <v>1</v>
@@ -68610,17 +68562,17 @@
       <c r="C1737" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1737" t="inlineStr">
+      <c r="D1737" t="inlineStr"/>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>AMPCO-PITTSBURGH CORP</t>
+        </is>
+      </c>
+      <c r="F1737" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1737" t="inlineStr">
-        <is>
-          <t>AMPCO-PITTSBURGH CORP</t>
-        </is>
-      </c>
-      <c r="F1737" t="inlineStr"/>
       <c r="G1737" t="inlineStr"/>
       <c r="H1737" t="n">
         <v>9</v>
@@ -68645,17 +68597,17 @@
       <c r="C1738" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1738" t="inlineStr">
+      <c r="D1738" t="inlineStr"/>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>TITAN MACHINERY INC</t>
+        </is>
+      </c>
+      <c r="F1738" t="inlineStr">
         <is>
           <t>TITN</t>
         </is>
       </c>
-      <c r="E1738" t="inlineStr">
-        <is>
-          <t>TITAN MACHINERY INC</t>
-        </is>
-      </c>
-      <c r="F1738" t="inlineStr"/>
       <c r="G1738" t="inlineStr"/>
       <c r="H1738" t="n">
         <v>1</v>
@@ -68680,17 +68632,17 @@
       <c r="C1739" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1739" t="inlineStr">
+      <c r="D1739" t="inlineStr"/>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="F1739" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1739" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="F1739" t="inlineStr"/>
       <c r="G1739" t="inlineStr"/>
       <c r="H1739" t="n">
         <v>2</v>
@@ -68715,17 +68667,17 @@
       <c r="C1740" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1740" t="inlineStr">
+      <c r="D1740" t="inlineStr"/>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>BASSETT FURNITURE INDS INC</t>
+        </is>
+      </c>
+      <c r="F1740" t="inlineStr">
         <is>
           <t>BSET</t>
         </is>
       </c>
-      <c r="E1740" t="inlineStr">
-        <is>
-          <t>BASSETT FURNITURE INDS INC</t>
-        </is>
-      </c>
-      <c r="F1740" t="inlineStr"/>
       <c r="G1740" t="inlineStr"/>
       <c r="H1740" t="n">
         <v>1</v>
@@ -68750,17 +68702,17 @@
       <c r="C1741" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1741" t="inlineStr">
+      <c r="D1741" t="inlineStr"/>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>ROCKY BRANDS INC</t>
+        </is>
+      </c>
+      <c r="F1741" t="inlineStr">
         <is>
           <t>RCKY</t>
         </is>
       </c>
-      <c r="E1741" t="inlineStr">
-        <is>
-          <t>ROCKY BRANDS INC</t>
-        </is>
-      </c>
-      <c r="F1741" t="inlineStr"/>
       <c r="G1741" t="inlineStr"/>
       <c r="H1741" t="n">
         <v>1</v>
@@ -68785,17 +68737,17 @@
       <c r="C1742" s="2" t="n">
         <v>45152</v>
       </c>
-      <c r="D1742" t="inlineStr">
+      <c r="D1742" t="inlineStr"/>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>COVENANT LOGISTICS GROUP INC  CLASS A COMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1742" t="inlineStr">
         <is>
           <t>CVLG</t>
         </is>
       </c>
-      <c r="E1742" t="inlineStr">
-        <is>
-          <t>COVENANT LOGISTICS GROUP INC  CLASS A COMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1742" t="inlineStr"/>
       <c r="G1742" t="inlineStr"/>
       <c r="H1742" t="n">
         <v>1</v>
@@ -68820,17 +68772,17 @@
       <c r="C1743" s="2" t="n">
         <v>45149</v>
       </c>
-      <c r="D1743" t="inlineStr">
+      <c r="D1743" t="inlineStr"/>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC       CASH DIV  ON       4 SHS      REC 07/21/23 PAY 08/11/23</t>
+        </is>
+      </c>
+      <c r="F1743" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1743" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC       CASH DIV  ON       4 SHS      REC 07/21/23 PAY 08/11/23</t>
-        </is>
-      </c>
-      <c r="F1743" t="inlineStr"/>
       <c r="G1743" t="inlineStr"/>
       <c r="H1743" t="n">
         <v>0</v>
@@ -68894,17 +68846,17 @@
       <c r="C1745" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1745" t="inlineStr">
+      <c r="D1745" t="inlineStr"/>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>KIMBALL ELECTRONICS INC       COM</t>
+        </is>
+      </c>
+      <c r="F1745" t="inlineStr">
         <is>
           <t>KE</t>
         </is>
       </c>
-      <c r="E1745" t="inlineStr">
-        <is>
-          <t>KIMBALL ELECTRONICS INC       COM</t>
-        </is>
-      </c>
-      <c r="F1745" t="inlineStr"/>
       <c r="G1745" t="inlineStr"/>
       <c r="H1745" t="n">
         <v>1</v>
@@ -68929,17 +68881,17 @@
       <c r="C1746" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1746" t="inlineStr">
+      <c r="D1746" t="inlineStr"/>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>CLARUS CORPORATION            COMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1746" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1746" t="inlineStr">
-        <is>
-          <t>CLARUS CORPORATION            COMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1746" t="inlineStr"/>
       <c r="G1746" t="inlineStr"/>
       <c r="H1746" t="n">
         <v>1</v>
@@ -68964,17 +68916,17 @@
       <c r="C1747" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1747" t="inlineStr">
+      <c r="D1747" t="inlineStr"/>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>VISHAY PRECISION GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1747" t="inlineStr">
         <is>
           <t>VPG</t>
         </is>
       </c>
-      <c r="E1747" t="inlineStr">
-        <is>
-          <t>VISHAY PRECISION GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1747" t="inlineStr"/>
       <c r="G1747" t="inlineStr"/>
       <c r="H1747" t="n">
         <v>1</v>
@@ -68999,17 +68951,17 @@
       <c r="C1748" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1748" t="inlineStr">
+      <c r="D1748" t="inlineStr"/>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>TITAN MACHINERY INC</t>
+        </is>
+      </c>
+      <c r="F1748" t="inlineStr">
         <is>
           <t>TITN</t>
         </is>
       </c>
-      <c r="E1748" t="inlineStr">
-        <is>
-          <t>TITAN MACHINERY INC</t>
-        </is>
-      </c>
-      <c r="F1748" t="inlineStr"/>
       <c r="G1748" t="inlineStr"/>
       <c r="H1748" t="n">
         <v>1</v>
@@ -69034,17 +68986,17 @@
       <c r="C1749" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1749" t="inlineStr">
+      <c r="D1749" t="inlineStr"/>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>LAKELAND INDS INC</t>
+        </is>
+      </c>
+      <c r="F1749" t="inlineStr">
         <is>
           <t>LAKE</t>
         </is>
       </c>
-      <c r="E1749" t="inlineStr">
-        <is>
-          <t>LAKELAND INDS INC</t>
-        </is>
-      </c>
-      <c r="F1749" t="inlineStr"/>
       <c r="G1749" t="inlineStr"/>
       <c r="H1749" t="n">
         <v>1</v>
@@ -69069,17 +69021,17 @@
       <c r="C1750" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1750" t="inlineStr">
+      <c r="D1750" t="inlineStr"/>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>NACCO INDUSTRIES INC-CL A</t>
+        </is>
+      </c>
+      <c r="F1750" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E1750" t="inlineStr">
-        <is>
-          <t>NACCO INDUSTRIES INC-CL A</t>
-        </is>
-      </c>
-      <c r="F1750" t="inlineStr"/>
       <c r="G1750" t="inlineStr"/>
       <c r="H1750" t="n">
         <v>1</v>
@@ -69104,17 +69056,17 @@
       <c r="C1751" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1751" t="inlineStr">
+      <c r="D1751" t="inlineStr"/>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>ROCKY BRANDS INC</t>
+        </is>
+      </c>
+      <c r="F1751" t="inlineStr">
         <is>
           <t>RCKY</t>
         </is>
       </c>
-      <c r="E1751" t="inlineStr">
-        <is>
-          <t>ROCKY BRANDS INC</t>
-        </is>
-      </c>
-      <c r="F1751" t="inlineStr"/>
       <c r="G1751" t="inlineStr"/>
       <c r="H1751" t="n">
         <v>1</v>
@@ -69139,17 +69091,17 @@
       <c r="C1752" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1752" t="inlineStr">
+      <c r="D1752" t="inlineStr"/>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>DUCOMMUN INC</t>
+        </is>
+      </c>
+      <c r="F1752" t="inlineStr">
         <is>
           <t>DCO</t>
         </is>
       </c>
-      <c r="E1752" t="inlineStr">
-        <is>
-          <t>DUCOMMUN INC</t>
-        </is>
-      </c>
-      <c r="F1752" t="inlineStr"/>
       <c r="G1752" t="inlineStr"/>
       <c r="H1752" t="n">
         <v>1</v>
@@ -69174,17 +69126,17 @@
       <c r="C1753" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1753" t="inlineStr">
+      <c r="D1753" t="inlineStr"/>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="F1753" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1753" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECHNOLOGIES INC</t>
-        </is>
-      </c>
-      <c r="F1753" t="inlineStr"/>
       <c r="G1753" t="inlineStr"/>
       <c r="H1753" t="n">
         <v>1</v>
@@ -69209,17 +69161,17 @@
       <c r="C1754" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1754" t="inlineStr">
+      <c r="D1754" t="inlineStr"/>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1754" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1754" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1754" t="inlineStr"/>
       <c r="G1754" t="inlineStr"/>
       <c r="H1754" t="n">
         <v>4</v>
@@ -69244,17 +69196,17 @@
       <c r="C1755" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1755" t="inlineStr">
+      <c r="D1755" t="inlineStr"/>
+      <c r="E1755" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES INC</t>
+        </is>
+      </c>
+      <c r="F1755" t="inlineStr">
         <is>
           <t>HURC</t>
         </is>
       </c>
-      <c r="E1755" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES INC</t>
-        </is>
-      </c>
-      <c r="F1755" t="inlineStr"/>
       <c r="G1755" t="inlineStr"/>
       <c r="H1755" t="n">
         <v>1</v>
@@ -69279,17 +69231,17 @@
       <c r="C1756" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1756" t="inlineStr">
+      <c r="D1756" t="inlineStr"/>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP</t>
+        </is>
+      </c>
+      <c r="F1756" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1756" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP</t>
-        </is>
-      </c>
-      <c r="F1756" t="inlineStr"/>
       <c r="G1756" t="inlineStr"/>
       <c r="H1756" t="n">
         <v>1</v>
@@ -69314,17 +69266,17 @@
       <c r="C1757" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1757" t="inlineStr">
+      <c r="D1757" t="inlineStr"/>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>ESCALADE INC</t>
+        </is>
+      </c>
+      <c r="F1757" t="inlineStr">
         <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="E1757" t="inlineStr">
-        <is>
-          <t>ESCALADE INC</t>
-        </is>
-      </c>
-      <c r="F1757" t="inlineStr"/>
       <c r="G1757" t="inlineStr"/>
       <c r="H1757" t="n">
         <v>1</v>
@@ -69349,17 +69301,17 @@
       <c r="C1758" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1758" t="inlineStr">
+      <c r="D1758" t="inlineStr"/>
+      <c r="E1758" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="F1758" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1758" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="F1758" t="inlineStr"/>
       <c r="G1758" t="inlineStr"/>
       <c r="H1758" t="n">
         <v>1</v>
@@ -69384,17 +69336,17 @@
       <c r="C1759" s="2" t="n">
         <v>45145</v>
       </c>
-      <c r="D1759" t="inlineStr">
+      <c r="D1759" t="inlineStr"/>
+      <c r="E1759" t="inlineStr">
+        <is>
+          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC                           CASH DIV  ON       3 SHS</t>
+        </is>
+      </c>
+      <c r="F1759" t="inlineStr">
         <is>
           <t>EBF</t>
         </is>
       </c>
-      <c r="E1759" t="inlineStr">
-        <is>
-          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC                           CASH DIV  ON       3 SHS</t>
-        </is>
-      </c>
-      <c r="F1759" t="inlineStr"/>
       <c r="G1759" t="inlineStr"/>
       <c r="H1759" t="n">
         <v>0</v>
@@ -69458,17 +69410,17 @@
       <c r="C1761" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="D1761" t="inlineStr">
+      <c r="D1761" t="inlineStr"/>
+      <c r="E1761" t="inlineStr">
+        <is>
+          <t>ESCALADE INC</t>
+        </is>
+      </c>
+      <c r="F1761" t="inlineStr">
         <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="E1761" t="inlineStr">
-        <is>
-          <t>ESCALADE INC</t>
-        </is>
-      </c>
-      <c r="F1761" t="inlineStr"/>
       <c r="G1761" t="inlineStr"/>
       <c r="H1761" t="n">
         <v>1</v>
@@ -69493,17 +69445,17 @@
       <c r="C1762" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="D1762" t="inlineStr">
+      <c r="D1762" t="inlineStr"/>
+      <c r="E1762" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP</t>
+        </is>
+      </c>
+      <c r="F1762" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1762" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP</t>
-        </is>
-      </c>
-      <c r="F1762" t="inlineStr"/>
       <c r="G1762" t="inlineStr"/>
       <c r="H1762" t="n">
         <v>2</v>
@@ -69528,17 +69480,17 @@
       <c r="C1763" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="D1763" t="inlineStr">
+      <c r="D1763" t="inlineStr"/>
+      <c r="E1763" t="inlineStr">
+        <is>
+          <t>CLARUS CORPORATION            COMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1763" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1763" t="inlineStr">
-        <is>
-          <t>CLARUS CORPORATION            COMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1763" t="inlineStr"/>
       <c r="G1763" t="inlineStr"/>
       <c r="H1763" t="n">
         <v>2</v>
@@ -69563,17 +69515,17 @@
       <c r="C1764" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="D1764" t="inlineStr">
+      <c r="D1764" t="inlineStr"/>
+      <c r="E1764" t="inlineStr">
+        <is>
+          <t>LAKELAND INDS INC</t>
+        </is>
+      </c>
+      <c r="F1764" t="inlineStr">
         <is>
           <t>LAKE</t>
         </is>
       </c>
-      <c r="E1764" t="inlineStr">
-        <is>
-          <t>LAKELAND INDS INC</t>
-        </is>
-      </c>
-      <c r="F1764" t="inlineStr"/>
       <c r="G1764" t="inlineStr"/>
       <c r="H1764" t="n">
         <v>1</v>
@@ -69598,17 +69550,17 @@
       <c r="C1765" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="D1765" t="inlineStr">
+      <c r="D1765" t="inlineStr"/>
+      <c r="E1765" t="inlineStr">
+        <is>
+          <t>AMPCO-PITTSBURGH CORP</t>
+        </is>
+      </c>
+      <c r="F1765" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1765" t="inlineStr">
-        <is>
-          <t>AMPCO-PITTSBURGH CORP</t>
-        </is>
-      </c>
-      <c r="F1765" t="inlineStr"/>
       <c r="G1765" t="inlineStr"/>
       <c r="H1765" t="n">
         <v>5</v>
@@ -69633,17 +69585,17 @@
       <c r="C1766" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="D1766" t="inlineStr">
+      <c r="D1766" t="inlineStr"/>
+      <c r="E1766" t="inlineStr">
+        <is>
+          <t>ROCKY BRANDS INC</t>
+        </is>
+      </c>
+      <c r="F1766" t="inlineStr">
         <is>
           <t>RCKY</t>
         </is>
       </c>
-      <c r="E1766" t="inlineStr">
-        <is>
-          <t>ROCKY BRANDS INC</t>
-        </is>
-      </c>
-      <c r="F1766" t="inlineStr"/>
       <c r="G1766" t="inlineStr"/>
       <c r="H1766" t="n">
         <v>1</v>
@@ -69668,17 +69620,17 @@
       <c r="C1767" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="D1767" t="inlineStr">
+      <c r="D1767" t="inlineStr"/>
+      <c r="E1767" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="F1767" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1767" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="F1767" t="inlineStr"/>
       <c r="G1767" t="inlineStr"/>
       <c r="H1767" t="n">
         <v>1</v>
@@ -69703,17 +69655,17 @@
       <c r="C1768" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="D1768" t="inlineStr">
+      <c r="D1768" t="inlineStr"/>
+      <c r="E1768" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="F1768" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1768" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECHNOLOGIES INC</t>
-        </is>
-      </c>
-      <c r="F1768" t="inlineStr"/>
       <c r="G1768" t="inlineStr"/>
       <c r="H1768" t="n">
         <v>1</v>
@@ -69738,17 +69690,17 @@
       <c r="C1769" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="D1769" t="inlineStr">
+      <c r="D1769" t="inlineStr"/>
+      <c r="E1769" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1769" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1769" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1769" t="inlineStr"/>
       <c r="G1769" t="inlineStr"/>
       <c r="H1769" t="n">
         <v>2</v>
@@ -69773,17 +69725,17 @@
       <c r="C1770" s="2" t="n">
         <v>45133</v>
       </c>
-      <c r="D1770" t="inlineStr">
+      <c r="D1770" t="inlineStr"/>
+      <c r="E1770" t="inlineStr">
+        <is>
+          <t>VSE CORP                      CASH DIV  ON       2 SHS      REC 07/12/23 PAY 07/26/23</t>
+        </is>
+      </c>
+      <c r="F1770" t="inlineStr">
         <is>
           <t>VSEC</t>
         </is>
       </c>
-      <c r="E1770" t="inlineStr">
-        <is>
-          <t>VSE CORP                      CASH DIV  ON       2 SHS      REC 07/12/23 PAY 07/26/23</t>
-        </is>
-      </c>
-      <c r="F1770" t="inlineStr"/>
       <c r="G1770" t="inlineStr"/>
       <c r="H1770" t="n">
         <v>0</v>
@@ -69808,17 +69760,17 @@
       <c r="C1771" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1771" t="inlineStr">
+      <c r="D1771" t="inlineStr"/>
+      <c r="E1771" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP</t>
+        </is>
+      </c>
+      <c r="F1771" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1771" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP</t>
-        </is>
-      </c>
-      <c r="F1771" t="inlineStr"/>
       <c r="G1771" t="inlineStr"/>
       <c r="H1771" t="n">
         <v>2</v>
@@ -69843,17 +69795,17 @@
       <c r="C1772" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1772" t="inlineStr">
+      <c r="D1772" t="inlineStr"/>
+      <c r="E1772" t="inlineStr">
+        <is>
+          <t>VISHAY PRECISION GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1772" t="inlineStr">
         <is>
           <t>VPG</t>
         </is>
       </c>
-      <c r="E1772" t="inlineStr">
-        <is>
-          <t>VISHAY PRECISION GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1772" t="inlineStr"/>
       <c r="G1772" t="inlineStr"/>
       <c r="H1772" t="n">
         <v>1</v>
@@ -69878,17 +69830,17 @@
       <c r="C1773" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1773" t="inlineStr">
+      <c r="D1773" t="inlineStr"/>
+      <c r="E1773" t="inlineStr">
+        <is>
+          <t>ROCKY BRANDS INC</t>
+        </is>
+      </c>
+      <c r="F1773" t="inlineStr">
         <is>
           <t>RCKY</t>
         </is>
       </c>
-      <c r="E1773" t="inlineStr">
-        <is>
-          <t>ROCKY BRANDS INC</t>
-        </is>
-      </c>
-      <c r="F1773" t="inlineStr"/>
       <c r="G1773" t="inlineStr"/>
       <c r="H1773" t="n">
         <v>1</v>
@@ -69913,17 +69865,17 @@
       <c r="C1774" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1774" t="inlineStr">
+      <c r="D1774" t="inlineStr"/>
+      <c r="E1774" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES INC</t>
+        </is>
+      </c>
+      <c r="F1774" t="inlineStr">
         <is>
           <t>HURC</t>
         </is>
       </c>
-      <c r="E1774" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES INC</t>
-        </is>
-      </c>
-      <c r="F1774" t="inlineStr"/>
       <c r="G1774" t="inlineStr"/>
       <c r="H1774" t="n">
         <v>1</v>
@@ -69948,17 +69900,17 @@
       <c r="C1775" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1775" t="inlineStr">
+      <c r="D1775" t="inlineStr"/>
+      <c r="E1775" t="inlineStr">
+        <is>
+          <t>LAKELAND INDS INC</t>
+        </is>
+      </c>
+      <c r="F1775" t="inlineStr">
         <is>
           <t>LAKE</t>
         </is>
       </c>
-      <c r="E1775" t="inlineStr">
-        <is>
-          <t>LAKELAND INDS INC</t>
-        </is>
-      </c>
-      <c r="F1775" t="inlineStr"/>
       <c r="G1775" t="inlineStr"/>
       <c r="H1775" t="n">
         <v>1</v>
@@ -69983,17 +69935,17 @@
       <c r="C1776" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1776" t="inlineStr">
+      <c r="D1776" t="inlineStr"/>
+      <c r="E1776" t="inlineStr">
+        <is>
+          <t>DUCOMMUN INC</t>
+        </is>
+      </c>
+      <c r="F1776" t="inlineStr">
         <is>
           <t>DCO</t>
         </is>
       </c>
-      <c r="E1776" t="inlineStr">
-        <is>
-          <t>DUCOMMUN INC</t>
-        </is>
-      </c>
-      <c r="F1776" t="inlineStr"/>
       <c r="G1776" t="inlineStr"/>
       <c r="H1776" t="n">
         <v>1</v>
@@ -70018,17 +69970,17 @@
       <c r="C1777" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1777" t="inlineStr">
+      <c r="D1777" t="inlineStr"/>
+      <c r="E1777" t="inlineStr">
+        <is>
+          <t>NACCO INDUSTRIES INC-CL A</t>
+        </is>
+      </c>
+      <c r="F1777" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E1777" t="inlineStr">
-        <is>
-          <t>NACCO INDUSTRIES INC-CL A</t>
-        </is>
-      </c>
-      <c r="F1777" t="inlineStr"/>
       <c r="G1777" t="inlineStr"/>
       <c r="H1777" t="n">
         <v>1</v>
@@ -70053,17 +70005,17 @@
       <c r="C1778" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1778" t="inlineStr">
+      <c r="D1778" t="inlineStr"/>
+      <c r="E1778" t="inlineStr">
+        <is>
+          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
+        </is>
+      </c>
+      <c r="F1778" t="inlineStr">
         <is>
           <t>EBF</t>
         </is>
       </c>
-      <c r="E1778" t="inlineStr">
-        <is>
-          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
-        </is>
-      </c>
-      <c r="F1778" t="inlineStr"/>
       <c r="G1778" t="inlineStr"/>
       <c r="H1778" t="n">
         <v>1</v>
@@ -70088,17 +70040,17 @@
       <c r="C1779" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1779" t="inlineStr">
+      <c r="D1779" t="inlineStr"/>
+      <c r="E1779" t="inlineStr">
+        <is>
+          <t>ESCALADE INC</t>
+        </is>
+      </c>
+      <c r="F1779" t="inlineStr">
         <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="E1779" t="inlineStr">
-        <is>
-          <t>ESCALADE INC</t>
-        </is>
-      </c>
-      <c r="F1779" t="inlineStr"/>
       <c r="G1779" t="inlineStr"/>
       <c r="H1779" t="n">
         <v>1</v>
@@ -70123,17 +70075,17 @@
       <c r="C1780" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1780" t="inlineStr">
+      <c r="D1780" t="inlineStr"/>
+      <c r="E1780" t="inlineStr">
+        <is>
+          <t>CLARUS CORPORATION            COMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1780" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1780" t="inlineStr">
-        <is>
-          <t>CLARUS CORPORATION            COMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1780" t="inlineStr"/>
       <c r="G1780" t="inlineStr"/>
       <c r="H1780" t="n">
         <v>2</v>
@@ -70158,17 +70110,17 @@
       <c r="C1781" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1781" t="inlineStr">
+      <c r="D1781" t="inlineStr"/>
+      <c r="E1781" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="F1781" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1781" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="F1781" t="inlineStr"/>
       <c r="G1781" t="inlineStr"/>
       <c r="H1781" t="n">
         <v>1</v>
@@ -70193,17 +70145,17 @@
       <c r="C1782" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1782" t="inlineStr">
+      <c r="D1782" t="inlineStr"/>
+      <c r="E1782" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1782" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1782" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1782" t="inlineStr"/>
       <c r="G1782" t="inlineStr"/>
       <c r="H1782" t="n">
         <v>2</v>
@@ -70228,17 +70180,17 @@
       <c r="C1783" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="D1783" t="inlineStr">
+      <c r="D1783" t="inlineStr"/>
+      <c r="E1783" t="inlineStr">
+        <is>
+          <t>AMPCO-PITTSBURGH CORP</t>
+        </is>
+      </c>
+      <c r="F1783" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1783" t="inlineStr">
-        <is>
-          <t>AMPCO-PITTSBURGH CORP</t>
-        </is>
-      </c>
-      <c r="F1783" t="inlineStr"/>
       <c r="G1783" t="inlineStr"/>
       <c r="H1783" t="n">
         <v>4</v>
@@ -70263,17 +70215,17 @@
       <c r="C1784" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1784" t="inlineStr">
+      <c r="D1784" t="inlineStr"/>
+      <c r="E1784" t="inlineStr">
+        <is>
+          <t>VOXX INTERNATIONAL CORPORATIONCLASS A</t>
+        </is>
+      </c>
+      <c r="F1784" t="inlineStr">
         <is>
           <t>VOXX</t>
         </is>
       </c>
-      <c r="E1784" t="inlineStr">
-        <is>
-          <t>VOXX INTERNATIONAL CORPORATIONCLASS A</t>
-        </is>
-      </c>
-      <c r="F1784" t="inlineStr"/>
       <c r="G1784" t="inlineStr"/>
       <c r="H1784" t="n">
         <v>-22</v>
@@ -70298,17 +70250,17 @@
       <c r="C1785" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1785" t="inlineStr">
+      <c r="D1785" t="inlineStr"/>
+      <c r="E1785" t="inlineStr">
+        <is>
+          <t>TITAN MACHINERY INC</t>
+        </is>
+      </c>
+      <c r="F1785" t="inlineStr">
         <is>
           <t>TITN</t>
         </is>
       </c>
-      <c r="E1785" t="inlineStr">
-        <is>
-          <t>TITAN MACHINERY INC</t>
-        </is>
-      </c>
-      <c r="F1785" t="inlineStr"/>
       <c r="G1785" t="inlineStr"/>
       <c r="H1785" t="n">
         <v>1</v>
@@ -70333,17 +70285,17 @@
       <c r="C1786" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1786" t="inlineStr">
+      <c r="D1786" t="inlineStr"/>
+      <c r="E1786" t="inlineStr">
+        <is>
+          <t>HOOKER FURNISHINGS CORPORATIONCOMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1786" t="inlineStr">
         <is>
           <t>HOFT</t>
         </is>
       </c>
-      <c r="E1786" t="inlineStr">
-        <is>
-          <t>HOOKER FURNISHINGS CORPORATIONCOMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1786" t="inlineStr"/>
       <c r="G1786" t="inlineStr"/>
       <c r="H1786" t="n">
         <v>-3</v>
@@ -70368,17 +70320,17 @@
       <c r="C1787" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1787" t="inlineStr">
+      <c r="D1787" t="inlineStr"/>
+      <c r="E1787" t="inlineStr">
+        <is>
+          <t>ESCALADE INC</t>
+        </is>
+      </c>
+      <c r="F1787" t="inlineStr">
         <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="E1787" t="inlineStr">
-        <is>
-          <t>ESCALADE INC</t>
-        </is>
-      </c>
-      <c r="F1787" t="inlineStr"/>
       <c r="G1787" t="inlineStr"/>
       <c r="H1787" t="n">
         <v>1</v>
@@ -70403,17 +70355,17 @@
       <c r="C1788" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1788" t="inlineStr">
+      <c r="D1788" t="inlineStr"/>
+      <c r="E1788" t="inlineStr">
+        <is>
+          <t>VSE CORP</t>
+        </is>
+      </c>
+      <c r="F1788" t="inlineStr">
         <is>
           <t>VSEC</t>
         </is>
       </c>
-      <c r="E1788" t="inlineStr">
-        <is>
-          <t>VSE CORP</t>
-        </is>
-      </c>
-      <c r="F1788" t="inlineStr"/>
       <c r="G1788" t="inlineStr"/>
       <c r="H1788" t="n">
         <v>1</v>
@@ -70438,17 +70390,17 @@
       <c r="C1789" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1789" t="inlineStr">
+      <c r="D1789" t="inlineStr"/>
+      <c r="E1789" t="inlineStr">
+        <is>
+          <t>SIGMATRON INTERNATIONAL INC</t>
+        </is>
+      </c>
+      <c r="F1789" t="inlineStr">
         <is>
           <t>SGMA</t>
         </is>
       </c>
-      <c r="E1789" t="inlineStr">
-        <is>
-          <t>SIGMATRON INTERNATIONAL INC</t>
-        </is>
-      </c>
-      <c r="F1789" t="inlineStr"/>
       <c r="G1789" t="inlineStr"/>
       <c r="H1789" t="n">
         <v>-71</v>
@@ -70473,17 +70425,17 @@
       <c r="C1790" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1790" t="inlineStr">
+      <c r="D1790" t="inlineStr"/>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>AMPCO-PITTSBURGH CORP</t>
+        </is>
+      </c>
+      <c r="F1790" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1790" t="inlineStr">
-        <is>
-          <t>AMPCO-PITTSBURGH CORP</t>
-        </is>
-      </c>
-      <c r="F1790" t="inlineStr"/>
       <c r="G1790" t="inlineStr"/>
       <c r="H1790" t="n">
         <v>3</v>
@@ -70508,17 +70460,17 @@
       <c r="C1791" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1791" t="inlineStr">
+      <c r="D1791" t="inlineStr"/>
+      <c r="E1791" t="inlineStr">
+        <is>
+          <t>KIMBALL ELECTRONICS INC       COM</t>
+        </is>
+      </c>
+      <c r="F1791" t="inlineStr">
         <is>
           <t>KE</t>
         </is>
       </c>
-      <c r="E1791" t="inlineStr">
-        <is>
-          <t>KIMBALL ELECTRONICS INC       COM</t>
-        </is>
-      </c>
-      <c r="F1791" t="inlineStr"/>
       <c r="G1791" t="inlineStr"/>
       <c r="H1791" t="n">
         <v>1</v>
@@ -70543,17 +70495,17 @@
       <c r="C1792" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1792" t="inlineStr">
+      <c r="D1792" t="inlineStr"/>
+      <c r="E1792" t="inlineStr">
+        <is>
+          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
+        </is>
+      </c>
+      <c r="F1792" t="inlineStr">
         <is>
           <t>EBF</t>
         </is>
       </c>
-      <c r="E1792" t="inlineStr">
-        <is>
-          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
-        </is>
-      </c>
-      <c r="F1792" t="inlineStr"/>
       <c r="G1792" t="inlineStr"/>
       <c r="H1792" t="n">
         <v>1</v>
@@ -70578,17 +70530,17 @@
       <c r="C1793" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1793" t="inlineStr">
+      <c r="D1793" t="inlineStr"/>
+      <c r="E1793" t="inlineStr">
+        <is>
+          <t>LAKELAND INDS INC</t>
+        </is>
+      </c>
+      <c r="F1793" t="inlineStr">
         <is>
           <t>LAKE</t>
         </is>
       </c>
-      <c r="E1793" t="inlineStr">
-        <is>
-          <t>LAKELAND INDS INC</t>
-        </is>
-      </c>
-      <c r="F1793" t="inlineStr"/>
       <c r="G1793" t="inlineStr"/>
       <c r="H1793" t="n">
         <v>2</v>
@@ -70613,17 +70565,17 @@
       <c r="C1794" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1794" t="inlineStr">
+      <c r="D1794" t="inlineStr"/>
+      <c r="E1794" t="inlineStr">
+        <is>
+          <t>BEAZER HOMES USA INC</t>
+        </is>
+      </c>
+      <c r="F1794" t="inlineStr">
         <is>
           <t>BZH</t>
         </is>
       </c>
-      <c r="E1794" t="inlineStr">
-        <is>
-          <t>BEAZER HOMES USA INC</t>
-        </is>
-      </c>
-      <c r="F1794" t="inlineStr"/>
       <c r="G1794" t="inlineStr"/>
       <c r="H1794" t="n">
         <v>1</v>
@@ -70648,17 +70600,17 @@
       <c r="C1795" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1795" t="inlineStr">
+      <c r="D1795" t="inlineStr"/>
+      <c r="E1795" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="F1795" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1795" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="F1795" t="inlineStr"/>
       <c r="G1795" t="inlineStr"/>
       <c r="H1795" t="n">
         <v>1</v>
@@ -70683,17 +70635,17 @@
       <c r="C1796" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1796" t="inlineStr">
+      <c r="D1796" t="inlineStr"/>
+      <c r="E1796" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1796" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1796" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1796" t="inlineStr"/>
       <c r="G1796" t="inlineStr"/>
       <c r="H1796" t="n">
         <v>2</v>
@@ -70718,17 +70670,17 @@
       <c r="C1797" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="D1797" t="inlineStr">
+      <c r="D1797" t="inlineStr"/>
+      <c r="E1797" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="F1797" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1797" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECHNOLOGIES INC</t>
-        </is>
-      </c>
-      <c r="F1797" t="inlineStr"/>
       <c r="G1797" t="inlineStr"/>
       <c r="H1797" t="n">
         <v>1</v>
@@ -70753,17 +70705,17 @@
       <c r="C1798" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1798" t="inlineStr">
+      <c r="D1798" t="inlineStr"/>
+      <c r="E1798" t="inlineStr">
+        <is>
+          <t>AMPCO-PITTSBURGH CORP</t>
+        </is>
+      </c>
+      <c r="F1798" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1798" t="inlineStr">
-        <is>
-          <t>AMPCO-PITTSBURGH CORP</t>
-        </is>
-      </c>
-      <c r="F1798" t="inlineStr"/>
       <c r="G1798" t="inlineStr"/>
       <c r="H1798" t="n">
         <v>3</v>
@@ -70788,17 +70740,17 @@
       <c r="C1799" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1799" t="inlineStr">
+      <c r="D1799" t="inlineStr"/>
+      <c r="E1799" t="inlineStr">
+        <is>
+          <t>CLARUS CORPORATION            COMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1799" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1799" t="inlineStr">
-        <is>
-          <t>CLARUS CORPORATION            COMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1799" t="inlineStr"/>
       <c r="G1799" t="inlineStr"/>
       <c r="H1799" t="n">
         <v>2</v>
@@ -70823,17 +70775,17 @@
       <c r="C1800" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1800" t="inlineStr">
+      <c r="D1800" t="inlineStr"/>
+      <c r="E1800" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP</t>
+        </is>
+      </c>
+      <c r="F1800" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1800" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP</t>
-        </is>
-      </c>
-      <c r="F1800" t="inlineStr"/>
       <c r="G1800" t="inlineStr"/>
       <c r="H1800" t="n">
         <v>1</v>
@@ -70858,17 +70810,17 @@
       <c r="C1801" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1801" t="inlineStr">
+      <c r="D1801" t="inlineStr"/>
+      <c r="E1801" t="inlineStr">
+        <is>
+          <t>ESCALADE INC</t>
+        </is>
+      </c>
+      <c r="F1801" t="inlineStr">
         <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="E1801" t="inlineStr">
-        <is>
-          <t>ESCALADE INC</t>
-        </is>
-      </c>
-      <c r="F1801" t="inlineStr"/>
       <c r="G1801" t="inlineStr"/>
       <c r="H1801" t="n">
         <v>1</v>
@@ -70893,17 +70845,17 @@
       <c r="C1802" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1802" t="inlineStr">
+      <c r="D1802" t="inlineStr"/>
+      <c r="E1802" t="inlineStr">
+        <is>
+          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
+        </is>
+      </c>
+      <c r="F1802" t="inlineStr">
         <is>
           <t>EBF</t>
         </is>
       </c>
-      <c r="E1802" t="inlineStr">
-        <is>
-          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
-        </is>
-      </c>
-      <c r="F1802" t="inlineStr"/>
       <c r="G1802" t="inlineStr"/>
       <c r="H1802" t="n">
         <v>1</v>
@@ -70928,17 +70880,17 @@
       <c r="C1803" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1803" t="inlineStr">
+      <c r="D1803" t="inlineStr"/>
+      <c r="E1803" t="inlineStr">
+        <is>
+          <t>TITAN MACHINERY INC</t>
+        </is>
+      </c>
+      <c r="F1803" t="inlineStr">
         <is>
           <t>TITN</t>
         </is>
       </c>
-      <c r="E1803" t="inlineStr">
-        <is>
-          <t>TITAN MACHINERY INC</t>
-        </is>
-      </c>
-      <c r="F1803" t="inlineStr"/>
       <c r="G1803" t="inlineStr"/>
       <c r="H1803" t="n">
         <v>1</v>
@@ -70963,17 +70915,17 @@
       <c r="C1804" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1804" t="inlineStr">
+      <c r="D1804" t="inlineStr"/>
+      <c r="E1804" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="F1804" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1804" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="F1804" t="inlineStr"/>
       <c r="G1804" t="inlineStr"/>
       <c r="H1804" t="n">
         <v>1</v>
@@ -70998,17 +70950,17 @@
       <c r="C1805" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1805" t="inlineStr">
+      <c r="D1805" t="inlineStr"/>
+      <c r="E1805" t="inlineStr">
+        <is>
+          <t>BEAZER HOMES USA INC</t>
+        </is>
+      </c>
+      <c r="F1805" t="inlineStr">
         <is>
           <t>BZH</t>
         </is>
       </c>
-      <c r="E1805" t="inlineStr">
-        <is>
-          <t>BEAZER HOMES USA INC</t>
-        </is>
-      </c>
-      <c r="F1805" t="inlineStr"/>
       <c r="G1805" t="inlineStr"/>
       <c r="H1805" t="n">
         <v>1</v>
@@ -71033,17 +70985,17 @@
       <c r="C1806" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1806" t="inlineStr">
+      <c r="D1806" t="inlineStr"/>
+      <c r="E1806" t="inlineStr">
+        <is>
+          <t>NACCO INDUSTRIES INC-CL A</t>
+        </is>
+      </c>
+      <c r="F1806" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E1806" t="inlineStr">
-        <is>
-          <t>NACCO INDUSTRIES INC-CL A</t>
-        </is>
-      </c>
-      <c r="F1806" t="inlineStr"/>
       <c r="G1806" t="inlineStr"/>
       <c r="H1806" t="n">
         <v>1</v>
@@ -71068,17 +71020,17 @@
       <c r="C1807" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1807" t="inlineStr">
+      <c r="D1807" t="inlineStr"/>
+      <c r="E1807" t="inlineStr">
+        <is>
+          <t>VISHAY PRECISION GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1807" t="inlineStr">
         <is>
           <t>VPG</t>
         </is>
       </c>
-      <c r="E1807" t="inlineStr">
-        <is>
-          <t>VISHAY PRECISION GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1807" t="inlineStr"/>
       <c r="G1807" t="inlineStr"/>
       <c r="H1807" t="n">
         <v>1</v>
@@ -71103,17 +71055,17 @@
       <c r="C1808" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1808" t="inlineStr">
+      <c r="D1808" t="inlineStr"/>
+      <c r="E1808" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="F1808" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1808" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECHNOLOGIES INC</t>
-        </is>
-      </c>
-      <c r="F1808" t="inlineStr"/>
       <c r="G1808" t="inlineStr"/>
       <c r="H1808" t="n">
         <v>1</v>
@@ -71138,17 +71090,17 @@
       <c r="C1809" s="2" t="n">
         <v>45117</v>
       </c>
-      <c r="D1809" t="inlineStr">
+      <c r="D1809" t="inlineStr"/>
+      <c r="E1809" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES INC           CASH DIV  ON       4 SHS      REC 06/26/23 PAY 07/10/23</t>
+        </is>
+      </c>
+      <c r="F1809" t="inlineStr">
         <is>
           <t>HURC</t>
         </is>
       </c>
-      <c r="E1809" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES INC           CASH DIV  ON       4 SHS      REC 06/26/23 PAY 07/10/23</t>
-        </is>
-      </c>
-      <c r="F1809" t="inlineStr"/>
       <c r="G1809" t="inlineStr"/>
       <c r="H1809" t="n">
         <v>0</v>
@@ -71173,17 +71125,17 @@
       <c r="C1810" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1810" t="inlineStr">
+      <c r="D1810" t="inlineStr"/>
+      <c r="E1810" t="inlineStr">
+        <is>
+          <t>CLARUS CORPORATION            COMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1810" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1810" t="inlineStr">
-        <is>
-          <t>CLARUS CORPORATION            COMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1810" t="inlineStr"/>
       <c r="G1810" t="inlineStr"/>
       <c r="H1810" t="n">
         <v>2</v>
@@ -71208,17 +71160,17 @@
       <c r="C1811" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1811" t="inlineStr">
+      <c r="D1811" t="inlineStr"/>
+      <c r="E1811" t="inlineStr">
+        <is>
+          <t>ESCALADE INC</t>
+        </is>
+      </c>
+      <c r="F1811" t="inlineStr">
         <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="E1811" t="inlineStr">
-        <is>
-          <t>ESCALADE INC</t>
-        </is>
-      </c>
-      <c r="F1811" t="inlineStr"/>
       <c r="G1811" t="inlineStr"/>
       <c r="H1811" t="n">
         <v>1</v>
@@ -71243,17 +71195,17 @@
       <c r="C1812" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1812" t="inlineStr">
+      <c r="D1812" t="inlineStr"/>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>KIMBALL ELECTRONICS INC       COM</t>
+        </is>
+      </c>
+      <c r="F1812" t="inlineStr">
         <is>
           <t>KE</t>
         </is>
       </c>
-      <c r="E1812" t="inlineStr">
-        <is>
-          <t>KIMBALL ELECTRONICS INC       COM</t>
-        </is>
-      </c>
-      <c r="F1812" t="inlineStr"/>
       <c r="G1812" t="inlineStr"/>
       <c r="H1812" t="n">
         <v>1</v>
@@ -71278,17 +71230,17 @@
       <c r="C1813" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1813" t="inlineStr">
+      <c r="D1813" t="inlineStr"/>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>LAKELAND INDS INC</t>
+        </is>
+      </c>
+      <c r="F1813" t="inlineStr">
         <is>
           <t>LAKE</t>
         </is>
       </c>
-      <c r="E1813" t="inlineStr">
-        <is>
-          <t>LAKELAND INDS INC</t>
-        </is>
-      </c>
-      <c r="F1813" t="inlineStr"/>
       <c r="G1813" t="inlineStr"/>
       <c r="H1813" t="n">
         <v>1</v>
@@ -71313,17 +71265,17 @@
       <c r="C1814" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1814" t="inlineStr">
+      <c r="D1814" t="inlineStr"/>
+      <c r="E1814" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="F1814" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1814" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="F1814" t="inlineStr"/>
       <c r="G1814" t="inlineStr"/>
       <c r="H1814" t="n">
         <v>1</v>
@@ -71348,17 +71300,17 @@
       <c r="C1815" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1815" t="inlineStr">
+      <c r="D1815" t="inlineStr"/>
+      <c r="E1815" t="inlineStr">
+        <is>
+          <t>HOOKER FURNISHINGS CORPORATIONCOMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1815" t="inlineStr">
         <is>
           <t>HOFT</t>
         </is>
       </c>
-      <c r="E1815" t="inlineStr">
-        <is>
-          <t>HOOKER FURNISHINGS CORPORATIONCOMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1815" t="inlineStr"/>
       <c r="G1815" t="inlineStr"/>
       <c r="H1815" t="n">
         <v>1</v>
@@ -71383,17 +71335,17 @@
       <c r="C1816" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1816" t="inlineStr">
+      <c r="D1816" t="inlineStr"/>
+      <c r="E1816" t="inlineStr">
+        <is>
+          <t>BEAZER HOMES USA INC</t>
+        </is>
+      </c>
+      <c r="F1816" t="inlineStr">
         <is>
           <t>BZH</t>
         </is>
       </c>
-      <c r="E1816" t="inlineStr">
-        <is>
-          <t>BEAZER HOMES USA INC</t>
-        </is>
-      </c>
-      <c r="F1816" t="inlineStr"/>
       <c r="G1816" t="inlineStr"/>
       <c r="H1816" t="n">
         <v>1</v>
@@ -71418,17 +71370,17 @@
       <c r="C1817" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1817" t="inlineStr">
+      <c r="D1817" t="inlineStr"/>
+      <c r="E1817" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES INC</t>
+        </is>
+      </c>
+      <c r="F1817" t="inlineStr">
         <is>
           <t>HURC</t>
         </is>
       </c>
-      <c r="E1817" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES INC</t>
-        </is>
-      </c>
-      <c r="F1817" t="inlineStr"/>
       <c r="G1817" t="inlineStr"/>
       <c r="H1817" t="n">
         <v>1</v>
@@ -71453,17 +71405,17 @@
       <c r="C1818" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1818" t="inlineStr">
+      <c r="D1818" t="inlineStr"/>
+      <c r="E1818" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="F1818" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1818" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECHNOLOGIES INC</t>
-        </is>
-      </c>
-      <c r="F1818" t="inlineStr"/>
       <c r="G1818" t="inlineStr"/>
       <c r="H1818" t="n">
         <v>1</v>
@@ -71488,17 +71440,17 @@
       <c r="C1819" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1819" t="inlineStr">
+      <c r="D1819" t="inlineStr"/>
+      <c r="E1819" t="inlineStr">
+        <is>
+          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
+        </is>
+      </c>
+      <c r="F1819" t="inlineStr">
         <is>
           <t>EBF</t>
         </is>
       </c>
-      <c r="E1819" t="inlineStr">
-        <is>
-          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
-        </is>
-      </c>
-      <c r="F1819" t="inlineStr"/>
       <c r="G1819" t="inlineStr"/>
       <c r="H1819" t="n">
         <v>1</v>
@@ -71523,17 +71475,17 @@
       <c r="C1820" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1820" t="inlineStr">
+      <c r="D1820" t="inlineStr"/>
+      <c r="E1820" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1820" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1820" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1820" t="inlineStr"/>
       <c r="G1820" t="inlineStr"/>
       <c r="H1820" t="n">
         <v>2</v>
@@ -71558,17 +71510,17 @@
       <c r="C1821" s="2" t="n">
         <v>45110</v>
       </c>
-      <c r="D1821" t="inlineStr">
+      <c r="D1821" t="inlineStr"/>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>AMPCO-PITTSBURGH CORP</t>
+        </is>
+      </c>
+      <c r="F1821" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1821" t="inlineStr">
-        <is>
-          <t>AMPCO-PITTSBURGH CORP</t>
-        </is>
-      </c>
-      <c r="F1821" t="inlineStr"/>
       <c r="G1821" t="inlineStr"/>
       <c r="H1821" t="n">
         <v>2</v>
@@ -71593,17 +71545,17 @@
       <c r="C1822" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="D1822" t="inlineStr">
+      <c r="D1822" t="inlineStr"/>
+      <c r="E1822" t="inlineStr">
+        <is>
+          <t>HOOKER FURNISHINGS CORPORATIONCOMMON STOCK                  CASH DIV  ON       2 SHS      REC 06/16/23 PAY 06/30/23</t>
+        </is>
+      </c>
+      <c r="F1822" t="inlineStr">
         <is>
           <t>HOFT</t>
         </is>
       </c>
-      <c r="E1822" t="inlineStr">
-        <is>
-          <t>HOOKER FURNISHINGS CORPORATIONCOMMON STOCK                  CASH DIV  ON       2 SHS      REC 06/16/23 PAY 06/30/23</t>
-        </is>
-      </c>
-      <c r="F1822" t="inlineStr"/>
       <c r="G1822" t="inlineStr"/>
       <c r="H1822" t="n">
         <v>0</v>
@@ -71628,17 +71580,17 @@
       <c r="C1823" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="D1823" t="inlineStr">
+      <c r="D1823" t="inlineStr"/>
+      <c r="E1823" t="inlineStr">
+        <is>
+          <t>COVENANT LOGISTICS GROUP INC  CLASS A COMMON STOCK          CASH DIV  ON       1 SHS      REC 06/02/23 PAY 06/30/23</t>
+        </is>
+      </c>
+      <c r="F1823" t="inlineStr">
         <is>
           <t>CVLG</t>
         </is>
       </c>
-      <c r="E1823" t="inlineStr">
-        <is>
-          <t>COVENANT LOGISTICS GROUP INC  CLASS A COMMON STOCK          CASH DIV  ON       1 SHS      REC 06/02/23 PAY 06/30/23</t>
-        </is>
-      </c>
-      <c r="F1823" t="inlineStr"/>
       <c r="G1823" t="inlineStr"/>
       <c r="H1823" t="n">
         <v>0</v>
@@ -71663,17 +71615,17 @@
       <c r="C1824" s="2" t="n">
         <v>45093</v>
       </c>
-      <c r="D1824" t="inlineStr">
+      <c r="D1824" t="inlineStr"/>
+      <c r="E1824" t="inlineStr">
+        <is>
+          <t>VSE CORP</t>
+        </is>
+      </c>
+      <c r="F1824" t="inlineStr">
         <is>
           <t>VSEC</t>
         </is>
       </c>
-      <c r="E1824" t="inlineStr">
-        <is>
-          <t>VSE CORP</t>
-        </is>
-      </c>
-      <c r="F1824" t="inlineStr"/>
       <c r="G1824" t="inlineStr"/>
       <c r="H1824" t="n">
         <v>1</v>
@@ -71698,17 +71650,17 @@
       <c r="C1825" s="2" t="n">
         <v>45093</v>
       </c>
-      <c r="D1825" t="inlineStr">
+      <c r="D1825" t="inlineStr"/>
+      <c r="E1825" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1825" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1825" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1825" t="inlineStr"/>
       <c r="G1825" t="inlineStr"/>
       <c r="H1825" t="n">
         <v>2</v>
@@ -72123,17 +72075,17 @@
       <c r="C1836" s="2" t="n">
         <v>45092</v>
       </c>
-      <c r="D1836" t="inlineStr">
+      <c r="D1836" t="inlineStr"/>
+      <c r="E1836" t="inlineStr">
+        <is>
+          <t>ROCKY BRANDS INC              CASH DIV  ON       2 SHS      REC 06/01/23 PAY 06/15/23</t>
+        </is>
+      </c>
+      <c r="F1836" t="inlineStr">
         <is>
           <t>RCKY</t>
         </is>
       </c>
-      <c r="E1836" t="inlineStr">
-        <is>
-          <t>ROCKY BRANDS INC              CASH DIV  ON       2 SHS      REC 06/01/23 PAY 06/15/23</t>
-        </is>
-      </c>
-      <c r="F1836" t="inlineStr"/>
       <c r="G1836" t="inlineStr"/>
       <c r="H1836" t="n">
         <v>0</v>
@@ -72158,17 +72110,17 @@
       <c r="C1837" s="2" t="n">
         <v>45092</v>
       </c>
-      <c r="D1837" t="inlineStr">
+      <c r="D1837" t="inlineStr"/>
+      <c r="E1837" t="inlineStr">
+        <is>
+          <t>***PANGAEA LOGISTICS SOLUTIONSLTD                           CASH DIV  ON     100 SHS      REC 06/01/23 PAY 06/15/23</t>
+        </is>
+      </c>
+      <c r="F1837" t="inlineStr">
         <is>
           <t>PANL</t>
         </is>
       </c>
-      <c r="E1837" t="inlineStr">
-        <is>
-          <t>***PANGAEA LOGISTICS SOLUTIONSLTD                           CASH DIV  ON     100 SHS      REC 06/01/23 PAY 06/15/23</t>
-        </is>
-      </c>
-      <c r="F1837" t="inlineStr"/>
       <c r="G1837" t="inlineStr"/>
       <c r="H1837" t="n">
         <v>0</v>
@@ -72193,17 +72145,17 @@
       <c r="C1838" s="2" t="n">
         <v>45092</v>
       </c>
-      <c r="D1838" t="inlineStr">
+      <c r="D1838" t="inlineStr"/>
+      <c r="E1838" t="inlineStr">
+        <is>
+          <t>NACCO INDUSTRIES INC-CL A     CASH DIV  ON       1 SHS      REC 05/31/23 PAY 06/15/23</t>
+        </is>
+      </c>
+      <c r="F1838" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E1838" t="inlineStr">
-        <is>
-          <t>NACCO INDUSTRIES INC-CL A     CASH DIV  ON       1 SHS      REC 05/31/23 PAY 06/15/23</t>
-        </is>
-      </c>
-      <c r="F1838" t="inlineStr"/>
       <c r="G1838" t="inlineStr"/>
       <c r="H1838" t="n">
         <v>0</v>
@@ -72228,17 +72180,17 @@
       <c r="C1839" s="2" t="n">
         <v>45092</v>
       </c>
-      <c r="D1839" t="inlineStr">
+      <c r="D1839" t="inlineStr"/>
+      <c r="E1839" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP     CASH DIV  ON       2 SHS      REC 06/01/23 PAY 06/15/23</t>
+        </is>
+      </c>
+      <c r="F1839" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1839" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP     CASH DIV  ON       2 SHS      REC 06/01/23 PAY 06/15/23</t>
-        </is>
-      </c>
-      <c r="F1839" t="inlineStr"/>
       <c r="G1839" t="inlineStr"/>
       <c r="H1839" t="n">
         <v>0</v>
@@ -72263,17 +72215,17 @@
       <c r="C1840" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1840" t="inlineStr">
+      <c r="D1840" t="inlineStr"/>
+      <c r="E1840" t="inlineStr">
+        <is>
+          <t>HOOKER FURNISHINGS CORPORATIONCOMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1840" t="inlineStr">
         <is>
           <t>HOFT</t>
         </is>
       </c>
-      <c r="E1840" t="inlineStr">
-        <is>
-          <t>HOOKER FURNISHINGS CORPORATIONCOMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1840" t="inlineStr"/>
       <c r="G1840" t="inlineStr"/>
       <c r="H1840" t="n">
         <v>1</v>
@@ -72298,17 +72250,17 @@
       <c r="C1841" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1841" t="inlineStr">
+      <c r="D1841" t="inlineStr"/>
+      <c r="E1841" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES INC</t>
+        </is>
+      </c>
+      <c r="F1841" t="inlineStr">
         <is>
           <t>HURC</t>
         </is>
       </c>
-      <c r="E1841" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES INC</t>
-        </is>
-      </c>
-      <c r="F1841" t="inlineStr"/>
       <c r="G1841" t="inlineStr"/>
       <c r="H1841" t="n">
         <v>1</v>
@@ -72333,17 +72285,17 @@
       <c r="C1842" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1842" t="inlineStr">
+      <c r="D1842" t="inlineStr"/>
+      <c r="E1842" t="inlineStr">
+        <is>
+          <t>BIG 5 SPORTING GOODS CORP</t>
+        </is>
+      </c>
+      <c r="F1842" t="inlineStr">
         <is>
           <t>BGFV</t>
         </is>
       </c>
-      <c r="E1842" t="inlineStr">
-        <is>
-          <t>BIG 5 SPORTING GOODS CORP</t>
-        </is>
-      </c>
-      <c r="F1842" t="inlineStr"/>
       <c r="G1842" t="inlineStr"/>
       <c r="H1842" t="n">
         <v>1</v>
@@ -72368,17 +72320,17 @@
       <c r="C1843" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1843" t="inlineStr">
+      <c r="D1843" t="inlineStr"/>
+      <c r="E1843" t="inlineStr">
+        <is>
+          <t>ESCALADE INC</t>
+        </is>
+      </c>
+      <c r="F1843" t="inlineStr">
         <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="E1843" t="inlineStr">
-        <is>
-          <t>ESCALADE INC</t>
-        </is>
-      </c>
-      <c r="F1843" t="inlineStr"/>
       <c r="G1843" t="inlineStr"/>
       <c r="H1843" t="n">
         <v>1</v>
@@ -72403,17 +72355,17 @@
       <c r="C1844" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1844" t="inlineStr">
+      <c r="D1844" t="inlineStr"/>
+      <c r="E1844" t="inlineStr">
+        <is>
+          <t>STRATTEC SECURITY CORP</t>
+        </is>
+      </c>
+      <c r="F1844" t="inlineStr">
         <is>
           <t>STRT</t>
         </is>
       </c>
-      <c r="E1844" t="inlineStr">
-        <is>
-          <t>STRATTEC SECURITY CORP</t>
-        </is>
-      </c>
-      <c r="F1844" t="inlineStr"/>
       <c r="G1844" t="inlineStr"/>
       <c r="H1844" t="n">
         <v>-3</v>
@@ -72438,17 +72390,17 @@
       <c r="C1845" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1845" t="inlineStr">
+      <c r="D1845" t="inlineStr"/>
+      <c r="E1845" t="inlineStr">
+        <is>
+          <t>COVENANT LOGISTICS GROUP INC  CLASS A COMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1845" t="inlineStr">
         <is>
           <t>CVLG</t>
         </is>
       </c>
-      <c r="E1845" t="inlineStr">
-        <is>
-          <t>COVENANT LOGISTICS GROUP INC  CLASS A COMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1845" t="inlineStr"/>
       <c r="G1845" t="inlineStr"/>
       <c r="H1845" t="n">
         <v>1</v>
@@ -72473,17 +72425,17 @@
       <c r="C1846" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1846" t="inlineStr">
+      <c r="D1846" t="inlineStr"/>
+      <c r="E1846" t="inlineStr">
+        <is>
+          <t>CLARUS CORPORATION            COMMON STOCK</t>
+        </is>
+      </c>
+      <c r="F1846" t="inlineStr">
         <is>
           <t>CLAR</t>
         </is>
       </c>
-      <c r="E1846" t="inlineStr">
-        <is>
-          <t>CLARUS CORPORATION            COMMON STOCK</t>
-        </is>
-      </c>
-      <c r="F1846" t="inlineStr"/>
       <c r="G1846" t="inlineStr"/>
       <c r="H1846" t="n">
         <v>1</v>
@@ -72508,17 +72460,17 @@
       <c r="C1847" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1847" t="inlineStr">
+      <c r="D1847" t="inlineStr"/>
+      <c r="E1847" t="inlineStr">
+        <is>
+          <t>DUCOMMUN INC</t>
+        </is>
+      </c>
+      <c r="F1847" t="inlineStr">
         <is>
           <t>DCO</t>
         </is>
       </c>
-      <c r="E1847" t="inlineStr">
-        <is>
-          <t>DUCOMMUN INC</t>
-        </is>
-      </c>
-      <c r="F1847" t="inlineStr"/>
       <c r="G1847" t="inlineStr"/>
       <c r="H1847" t="n">
         <v>1</v>
@@ -72543,17 +72495,17 @@
       <c r="C1848" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1848" t="inlineStr">
+      <c r="D1848" t="inlineStr"/>
+      <c r="E1848" t="inlineStr">
+        <is>
+          <t>VISHAY PRECISION GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1848" t="inlineStr">
         <is>
           <t>VPG</t>
         </is>
       </c>
-      <c r="E1848" t="inlineStr">
-        <is>
-          <t>VISHAY PRECISION GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1848" t="inlineStr"/>
       <c r="G1848" t="inlineStr"/>
       <c r="H1848" t="n">
         <v>1</v>
@@ -72578,17 +72530,17 @@
       <c r="C1849" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1849" t="inlineStr">
+      <c r="D1849" t="inlineStr"/>
+      <c r="E1849" t="inlineStr">
+        <is>
+          <t>ADVANCED EMISSIONS SOLUTIONS  INC COM</t>
+        </is>
+      </c>
+      <c r="F1849" t="inlineStr">
         <is>
           <t>ADES</t>
         </is>
       </c>
-      <c r="E1849" t="inlineStr">
-        <is>
-          <t>ADVANCED EMISSIONS SOLUTIONS  INC COM</t>
-        </is>
-      </c>
-      <c r="F1849" t="inlineStr"/>
       <c r="G1849" t="inlineStr"/>
       <c r="H1849" t="n">
         <v>-4</v>
@@ -72613,17 +72565,17 @@
       <c r="C1850" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1850" t="inlineStr">
+      <c r="D1850" t="inlineStr"/>
+      <c r="E1850" t="inlineStr">
+        <is>
+          <t>TITAN MACHINERY INC</t>
+        </is>
+      </c>
+      <c r="F1850" t="inlineStr">
         <is>
           <t>TITN</t>
         </is>
       </c>
-      <c r="E1850" t="inlineStr">
-        <is>
-          <t>TITAN MACHINERY INC</t>
-        </is>
-      </c>
-      <c r="F1850" t="inlineStr"/>
       <c r="G1850" t="inlineStr"/>
       <c r="H1850" t="n">
         <v>1</v>
@@ -72648,17 +72600,17 @@
       <c r="C1851" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1851" t="inlineStr">
+      <c r="D1851" t="inlineStr"/>
+      <c r="E1851" t="inlineStr">
+        <is>
+          <t>NACCO INDUSTRIES INC-CL A</t>
+        </is>
+      </c>
+      <c r="F1851" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="E1851" t="inlineStr">
-        <is>
-          <t>NACCO INDUSTRIES INC-CL A</t>
-        </is>
-      </c>
-      <c r="F1851" t="inlineStr"/>
       <c r="G1851" t="inlineStr"/>
       <c r="H1851" t="n">
         <v>1</v>
@@ -72683,17 +72635,17 @@
       <c r="C1852" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1852" t="inlineStr">
+      <c r="D1852" t="inlineStr"/>
+      <c r="E1852" t="inlineStr">
+        <is>
+          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
+        </is>
+      </c>
+      <c r="F1852" t="inlineStr">
         <is>
           <t>EBF</t>
         </is>
       </c>
-      <c r="E1852" t="inlineStr">
-        <is>
-          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC</t>
-        </is>
-      </c>
-      <c r="F1852" t="inlineStr"/>
       <c r="G1852" t="inlineStr"/>
       <c r="H1852" t="n">
         <v>1</v>
@@ -72718,17 +72670,17 @@
       <c r="C1853" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1853" t="inlineStr">
+      <c r="D1853" t="inlineStr"/>
+      <c r="E1853" t="inlineStr">
+        <is>
+          <t>MISTRAS GROUP INC</t>
+        </is>
+      </c>
+      <c r="F1853" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="E1853" t="inlineStr">
-        <is>
-          <t>MISTRAS GROUP INC</t>
-        </is>
-      </c>
-      <c r="F1853" t="inlineStr"/>
       <c r="G1853" t="inlineStr"/>
       <c r="H1853" t="n">
         <v>1</v>
@@ -72753,17 +72705,17 @@
       <c r="C1854" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1854" t="inlineStr">
+      <c r="D1854" t="inlineStr"/>
+      <c r="E1854" t="inlineStr">
+        <is>
+          <t>AMPCO-PITTSBURGH CORP</t>
+        </is>
+      </c>
+      <c r="F1854" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="E1854" t="inlineStr">
-        <is>
-          <t>AMPCO-PITTSBURGH CORP</t>
-        </is>
-      </c>
-      <c r="F1854" t="inlineStr"/>
       <c r="G1854" t="inlineStr"/>
       <c r="H1854" t="n">
         <v>3</v>
@@ -72788,17 +72740,17 @@
       <c r="C1855" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1855" t="inlineStr">
+      <c r="D1855" t="inlineStr"/>
+      <c r="E1855" t="inlineStr">
+        <is>
+          <t>CORE MOLDING TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="F1855" t="inlineStr">
         <is>
           <t>CMT</t>
         </is>
       </c>
-      <c r="E1855" t="inlineStr">
-        <is>
-          <t>CORE MOLDING TECHNOLOGIES INC</t>
-        </is>
-      </c>
-      <c r="F1855" t="inlineStr"/>
       <c r="G1855" t="inlineStr"/>
       <c r="H1855" t="n">
         <v>1</v>
@@ -72823,17 +72775,17 @@
       <c r="C1856" s="2" t="n">
         <v>45089</v>
       </c>
-      <c r="D1856" t="inlineStr">
+      <c r="D1856" t="inlineStr"/>
+      <c r="E1856" t="inlineStr">
+        <is>
+          <t>FRIEDMAN INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="F1856" t="inlineStr">
         <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="E1856" t="inlineStr">
-        <is>
-          <t>FRIEDMAN INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="F1856" t="inlineStr"/>
       <c r="G1856" t="inlineStr"/>
       <c r="H1856" t="n">
         <v>1</v>
@@ -72858,17 +72810,17 @@
       <c r="C1857" s="2" t="n">
         <v>45072</v>
       </c>
-      <c r="D1857" t="inlineStr">
+      <c r="D1857" t="inlineStr"/>
+      <c r="E1857" t="inlineStr">
+        <is>
+          <t>BASSETT FURNITURE INDS INC    CASH DIV  ON      13 SHS      REC 05/12/23 PAY 05/26/23</t>
+        </is>
+      </c>
+      <c r="F1857" t="inlineStr">
         <is>
           <t>BSET</t>
         </is>
       </c>
-      <c r="E1857" t="inlineStr">
-        <is>
-          <t>BASSETT FURNITURE INDS INC    CASH DIV  ON      13 SHS      REC 05/12/23 PAY 05/26/23</t>
-        </is>
-      </c>
-      <c r="F1857" t="inlineStr"/>
       <c r="G1857" t="inlineStr"/>
       <c r="H1857" t="n">
         <v>0</v>
@@ -72893,17 +72845,17 @@
       <c r="C1858" s="2" t="n">
         <v>45063</v>
       </c>
-      <c r="D1858" t="inlineStr">
+      <c r="D1858" t="inlineStr"/>
+      <c r="E1858" t="inlineStr">
+        <is>
+          <t>VSE CORP                      CASH DIV  ON       1 SHS      REC 05/03/23 PAY 05/17/23</t>
+        </is>
+      </c>
+      <c r="F1858" t="inlineStr">
         <is>
           <t>VSEC</t>
         </is>
       </c>
-      <c r="E1858" t="inlineStr">
-        <is>
-          <t>VSE CORP                      CASH DIV  ON       1 SHS      REC 05/03/23 PAY 05/17/23</t>
-        </is>
-      </c>
-      <c r="F1858" t="inlineStr"/>
       <c r="G1858" t="inlineStr"/>
       <c r="H1858" t="n">
         <v>0</v>
@@ -72928,17 +72880,17 @@
       <c r="C1859" s="2" t="n">
         <v>45054</v>
       </c>
-      <c r="D1859" t="inlineStr">
+      <c r="D1859" t="inlineStr"/>
+      <c r="E1859" t="inlineStr">
+        <is>
+          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC                           CASH DIV  ON       1 SHS</t>
+        </is>
+      </c>
+      <c r="F1859" t="inlineStr">
         <is>
           <t>EBF</t>
         </is>
       </c>
-      <c r="E1859" t="inlineStr">
-        <is>
-          <t>ENNIS INC                     FORMERLY ENNIS BUSINESS FORMS INC                           CASH DIV  ON       1 SHS</t>
-        </is>
-      </c>
-      <c r="F1859" t="inlineStr"/>
       <c r="G1859" t="inlineStr"/>
       <c r="H1859" t="n">
         <v>0</v>
@@ -72963,17 +72915,17 @@
       <c r="C1860" s="2" t="n">
         <v>45026</v>
       </c>
-      <c r="D1860" t="inlineStr">
+      <c r="D1860" t="inlineStr"/>
+      <c r="E1860" t="inlineStr">
+        <is>
+          <t>HURCO COMPANIES INC           CASH DIV  ON       3 SHS      REC 03/27/23 PAY 04/10/23</t>
+        </is>
+      </c>
+      <c r="F1860" t="inlineStr">
         <is>
           <t>HURC</t>
         </is>
       </c>
-      <c r="E1860" t="inlineStr">
-        <is>
-          <t>HURCO COMPANIES INC           CASH DIV  ON       3 SHS      REC 03/27/23 PAY 04/10/23</t>
-        </is>
-      </c>
-      <c r="F1860" t="inlineStr"/>
       <c r="G1860" t="inlineStr"/>
       <c r="H1860" t="n">
         <v>0</v>
